--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_PRD总表'!$A$1:$Y$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_阶段路线图'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_核心数据对象'!$A$1:$E$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_核心数据对象'!$A$1:$E$338</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_API与事件'!$A$1:$F$476</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_角色权限矩阵'!$A$2:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_测试与验收计划'!$A$1:$L$60</definedName>
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..092已完成，下一项PRD-093。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..093已完成，下一项PRD-094。</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Workspace、OrganizationProfile、PersonalProfile、WorkspaceRegion、WorkspaceProvisioningJob</t>
+          <t>Workspace、WorkspaceTenantBinding、WorkspaceMembership、OrganizationProfile、PersonalProfile、WorkspaceRegion、WorkspaceProvisioningJob、WorkspaceEnvironmentOrigin、WorkspaceEvent、WorkspaceEventOutbox、WorkspaceUserProjectionClaim</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>personal Workspace的owner仅本人；organization Workspace的owner可维护本企业；platform_ops只看脱敏生命周期</t>
+          <t>GlobalSession只允许已验证账号创建空间；personal/organization Workspace的owner仅本人可读写；本条不授予平台角色或其他成员权限</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>注册后可选择个人或企业；同一账号可安全切换多个空间；创建事务不会产生假Provider；失败可重试且不产生半初始化租户；业务表继续带tenant_id。</t>
+          <t>注册后可创建个人或企业空间；同一账号可创建并列出多个空间；创建事务不会产生假Provider；失败可重试且不产生半初始化租户；本条不签发WorkspaceSession。</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>将现有Tenant投影为organization Workspace；default租户保留但标记legacy_bootstrap；回滚不删除Workspace。</t>
+          <t>0085新增Workspace、不可变WorkspaceTenantBinding、owner foundation、Region/profile/provisioning/environment origin、event/outbox和一次性legacy User投影证明；现有Tenant确定性回填；pristine可down，新增安全事实原子阻断回滚。</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>slug防枚举、企业名输出转义、Region不可静默跨境、Owner不可孤儿、创建幂等。</t>
+          <t>GlobalSession与CSRF/Origin边界；Idempotency-Key只存HMAC并绑定规范body；slug冲突同形；企业名输出转义且不进日志/事件/幂等记录；Region允许列表失败关闭；Owner不可孤儿。</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -13867,7 +13867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E332"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>OrganizationProfile</t>
+          <t>WorkspaceTenantBinding</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PersonalProfile</t>
+          <t>WorkspaceMembership</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceRegion</t>
+          <t>OrganizationProfile</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceProvisioningJob</t>
+          <t>PersonalProfile</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -14582,12 +14582,12 @@
     <row r="27" ht="66" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>PRD-094</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceMembership</t>
+          <t>WorkspaceRegion</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -14609,12 +14609,12 @@
     <row r="28" ht="66" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>PRD-094</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceSession</t>
+          <t>WorkspaceProvisioningJob</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -14636,12 +14636,12 @@
     <row r="29" ht="66" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>PRD-094</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>OwnerTransfer</t>
+          <t>WorkspaceEnvironmentOrigin</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -14663,12 +14663,12 @@
     <row r="30" ht="66" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>PRD-094</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>MembershipRevision</t>
+          <t>WorkspaceEvent</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -14690,22 +14690,22 @@
     <row r="31" ht="66" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PlatformOperator</t>
+          <t>WorkspaceEventOutbox</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -14717,22 +14717,22 @@
     <row r="32" ht="66" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-093</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PlatformRole</t>
+          <t>WorkspaceUserProjectionClaim</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -14744,22 +14744,22 @@
     <row r="33" ht="66" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-094</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PlatformPermission</t>
+          <t>WorkspaceMembership</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -14771,12 +14771,12 @@
     <row r="34" ht="66" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-094</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>SupportGrant</t>
+          <t>WorkspaceSession</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -14798,12 +14798,12 @@
     <row r="35" ht="66" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-094</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>BreakGlassSession</t>
+          <t>OwnerTransfer</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -14825,22 +14825,22 @@
     <row r="36" ht="66" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>PRD-095</t>
+          <t>PRD-094</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PlatformAuditLog</t>
+          <t>MembershipRevision</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -14852,22 +14852,22 @@
     <row r="37" ht="66" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>PRD-096</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceOperationalState</t>
+          <t>PlatformOperator</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -14879,22 +14879,22 @@
     <row r="38" ht="66" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PRD-096</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceRiskTag</t>
+          <t>PlatformRole</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="39" ht="66" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PRD-096</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceHealthProjection</t>
+          <t>PlatformPermission</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -14933,22 +14933,22 @@
     <row r="40" ht="66" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PRD-096</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PlatformActionIntent</t>
+          <t>SupportGrant</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -14960,12 +14960,12 @@
     <row r="41" ht="66" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>PRD-097</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>OnboardingProgress</t>
+          <t>BreakGlassSession</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -14987,22 +14987,22 @@
     <row r="42" ht="66" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PRD-097</t>
+          <t>PRD-095</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>OnboardingStepFact</t>
+          <t>PlatformAuditLog</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -15014,12 +15014,12 @@
     <row r="43" ht="66" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>PRD-097</t>
+          <t>PRD-096</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>OnboardingAcknowledgement</t>
+          <t>WorkspaceOperationalState</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -15041,12 +15041,12 @@
     <row r="44" ht="66" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PRD-097</t>
+          <t>PRD-096</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ActivationCheckpoint</t>
+          <t>WorkspaceRiskTag</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -15068,22 +15068,22 @@
     <row r="45" ht="66" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-096</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PlanCatalog</t>
+          <t>WorkspaceHealthProjection</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -15095,12 +15095,12 @@
     <row r="46" ht="66" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-096</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PlanVersion</t>
+          <t>PlatformActionIntent</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -15122,12 +15122,12 @@
     <row r="47" ht="66" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-097</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>OnboardingProgress</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -15149,12 +15149,12 @@
     <row r="48" ht="66" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-097</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>EntitlementSnapshot</t>
+          <t>OnboardingStepFact</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -15176,12 +15176,12 @@
     <row r="49" ht="66" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-097</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>OnboardingAcknowledgement</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -15203,12 +15203,12 @@
     <row r="50" ht="66" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PRD-098</t>
+          <t>PRD-097</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OrderRecord</t>
+          <t>ActivationCheckpoint</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -15230,22 +15230,22 @@
     <row r="51" ht="66" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MeterDefinition</t>
+          <t>PlanCatalog</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -15257,22 +15257,22 @@
     <row r="52" ht="66" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MeterReading</t>
+          <t>PlanVersion</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -15284,12 +15284,12 @@
     <row r="53" ht="66" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>BillingCycle</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -15311,12 +15311,12 @@
     <row r="54" ht="66" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>QuotaAllocation</t>
+          <t>EntitlementSnapshot</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -15338,12 +15338,12 @@
     <row r="55" ht="66" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>BillingSummary</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -15365,12 +15365,12 @@
     <row r="56" ht="66" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PRD-099</t>
+          <t>PRD-098</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>BillingAdjustment</t>
+          <t>OrderRecord</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -15392,22 +15392,22 @@
     <row r="57" ht="66" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>DatabaseCluster</t>
+          <t>MeterDefinition</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -15419,22 +15419,22 @@
     <row r="58" ht="66" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CacheCluster</t>
+          <t>MeterReading</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -15446,22 +15446,22 @@
     <row r="59" ht="66" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ObjectStore</t>
+          <t>BillingCycle</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -15473,22 +15473,22 @@
     <row r="60" ht="66" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>KeyRing</t>
+          <t>QuotaAllocation</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -15500,12 +15500,12 @@
     <row r="61" ht="66" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>BackupSet</t>
+          <t>BillingSummary</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -15527,12 +15527,12 @@
     <row r="62" ht="66" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PRD-100</t>
+          <t>PRD-099</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>MigrationLease</t>
+          <t>BillingAdjustment</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -15554,12 +15554,12 @@
     <row r="63" ht="66" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>PRD-101</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>GatewayCell</t>
+          <t>DatabaseCluster</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -15581,22 +15581,22 @@
     <row r="64" ht="66" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PRD-101</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>WorkspacePlacement</t>
+          <t>CacheCluster</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -15608,22 +15608,22 @@
     <row r="65" ht="66" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>PRD-101</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>CapacityLease</t>
+          <t>ObjectStore</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -15635,22 +15635,22 @@
     <row r="66" ht="66" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>PRD-101</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ConfigSnapshotLease</t>
+          <t>KeyRing</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -15662,22 +15662,22 @@
     <row r="67" ht="66" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>PRD-101</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>GatewayRelease</t>
+          <t>BackupSet</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -15689,12 +15689,12 @@
     <row r="68" ht="66" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>PRD-102</t>
+          <t>PRD-100</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>LegalEntityProfile</t>
+          <t>MigrationLease</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -15716,22 +15716,22 @@
     <row r="69" ht="66" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PRD-102</t>
+          <t>PRD-101</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>BusinessVerificationIntent</t>
+          <t>GatewayCell</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -15743,12 +15743,12 @@
     <row r="70" ht="66" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>PRD-102</t>
+          <t>PRD-101</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>VerificationEvidence</t>
+          <t>WorkspacePlacement</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -15770,12 +15770,12 @@
     <row r="71" ht="66" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>PRD-102</t>
+          <t>PRD-101</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ContractProfile</t>
+          <t>CapacityLease</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -15797,12 +15797,12 @@
     <row r="72" ht="66" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>PRD-102</t>
+          <t>PRD-101</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>BillingProfile</t>
+          <t>ConfigSnapshotLease</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -15824,22 +15824,22 @@
     <row r="73" ht="66" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-101</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>SubscriptionOrder</t>
+          <t>GatewayRelease</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -15851,12 +15851,12 @@
     <row r="74" ht="66" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-102</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>PaymentIntent</t>
+          <t>LegalEntityProfile</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -15878,12 +15878,12 @@
     <row r="75" ht="66" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-102</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>PaymentAttempt</t>
+          <t>BusinessVerificationIntent</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -15905,12 +15905,12 @@
     <row r="76" ht="66" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-102</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>PaymentWebhookReceipt</t>
+          <t>VerificationEvidence</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -15932,12 +15932,12 @@
     <row r="77" ht="66" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-102</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Refund</t>
+          <t>ContractProfile</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -15959,12 +15959,12 @@
     <row r="78" ht="66" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>PRD-103</t>
+          <t>PRD-102</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>DunningCase</t>
+          <t>BillingProfile</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -15986,12 +15986,12 @@
     <row r="79" ht="66" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>PRD-104</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>BillingStatement</t>
+          <t>SubscriptionOrder</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -16013,12 +16013,12 @@
     <row r="80" ht="66" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>PRD-104</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>InvoiceRequest</t>
+          <t>PaymentIntent</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -16040,12 +16040,12 @@
     <row r="81" ht="66" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>PRD-104</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>InvoiceArtifact</t>
+          <t>PaymentAttempt</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -16067,12 +16067,12 @@
     <row r="82" ht="66" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>PRD-104</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>ReconciliationRun</t>
+          <t>PaymentWebhookReceipt</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -16094,12 +16094,12 @@
     <row r="83" ht="66" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>PRD-104</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ReconciliationDifference</t>
+          <t>Refund</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -16121,12 +16121,12 @@
     <row r="84" ht="66" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>PRD-105</t>
+          <t>PRD-103</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>DunningCase</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -16148,12 +16148,12 @@
     <row r="85" ht="66" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>PRD-105</t>
+          <t>PRD-104</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>NotificationTemplate</t>
+          <t>BillingStatement</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -16175,12 +16175,12 @@
     <row r="86" ht="66" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>PRD-105</t>
+          <t>PRD-104</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>NotificationPreference</t>
+          <t>InvoiceRequest</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -16202,12 +16202,12 @@
     <row r="87" ht="66" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>PRD-105</t>
+          <t>PRD-104</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>DeliveryAttempt</t>
+          <t>InvoiceArtifact</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -16229,12 +16229,12 @@
     <row r="88" ht="66" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>PRD-105</t>
+          <t>PRD-104</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ChannelSuppression</t>
+          <t>ReconciliationRun</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -16256,22 +16256,22 @@
     <row r="89" ht="66" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-104</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>PlatformJob</t>
+          <t>ReconciliationDifference</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -16283,12 +16283,12 @@
     <row r="90" ht="66" customHeight="1">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-105</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>JobAttempt</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -16310,12 +16310,12 @@
     <row r="91" ht="66" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-105</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>WorkQueue</t>
+          <t>NotificationTemplate</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -16337,12 +16337,12 @@
     <row r="92" ht="66" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-105</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>SchedulerLease</t>
+          <t>NotificationPreference</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -16364,12 +16364,12 @@
     <row r="93" ht="66" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-105</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>JobCheckpoint</t>
+          <t>DeliveryAttempt</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -16391,12 +16391,12 @@
     <row r="94" ht="66" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>PRD-106</t>
+          <t>PRD-105</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>DeadLetterJob</t>
+          <t>ChannelSuppression</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -16418,12 +16418,12 @@
     <row r="95" ht="66" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>FeatureFlag</t>
+          <t>PlatformJob</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -16445,22 +16445,22 @@
     <row r="96" ht="66" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>FlagVersion</t>
+          <t>JobAttempt</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -16472,12 +16472,12 @@
     <row r="97" ht="66" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>TenantCohort</t>
+          <t>WorkQueue</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -16499,12 +16499,12 @@
     <row r="98" ht="66" customHeight="1">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>FlagRollout</t>
+          <t>SchedulerLease</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -16526,12 +16526,12 @@
     <row r="99" ht="66" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>FlagEvaluationSnapshot</t>
+          <t>JobCheckpoint</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -16553,12 +16553,12 @@
     <row r="100" ht="66" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>PRD-107</t>
+          <t>PRD-106</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>FeatureExposure</t>
+          <t>DeadLetterJob</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -16580,22 +16580,22 @@
     <row r="101" ht="66" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>PRD-108</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>ConfigSnapshot</t>
+          <t>FeatureFlag</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -16607,22 +16607,22 @@
     <row r="102" ht="66" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>PRD-108</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>ConfigDelta</t>
+          <t>FlagVersion</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -16634,12 +16634,12 @@
     <row r="103" ht="66" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>PRD-108</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>ConfigAck</t>
+          <t>TenantCohort</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -16661,12 +16661,12 @@
     <row r="104" ht="66" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>PRD-108</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>CacheWatermark</t>
+          <t>FlagRollout</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -16688,12 +16688,12 @@
     <row r="105" ht="66" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>PRD-108</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>ConfigRebuildJob</t>
+          <t>FlagEvaluationSnapshot</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -16715,22 +16715,22 @@
     <row r="106" ht="66" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-107</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>ServiceCatalogEntry</t>
+          <t>FeatureExposure</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -16742,22 +16742,22 @@
     <row r="107" ht="66" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-108</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>ServiceLevelObjective</t>
+          <t>ConfigSnapshot</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -16769,22 +16769,22 @@
     <row r="108" ht="66" customHeight="1">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-108</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>ErrorBudget</t>
+          <t>ConfigDelta</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -16796,22 +16796,22 @@
     <row r="109" ht="66" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-108</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>ConfigAck</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -16823,22 +16823,22 @@
     <row r="110" ht="66" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-108</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>OnCallRoute</t>
+          <t>CacheWatermark</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -16850,12 +16850,12 @@
     <row r="111" ht="66" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>PRD-109</t>
+          <t>PRD-108</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>TelemetryPolicy</t>
+          <t>ConfigRebuildJob</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -16877,22 +16877,22 @@
     <row r="112" ht="66" customHeight="1">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>RiskSignal</t>
+          <t>ServiceCatalogEntry</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -16904,22 +16904,22 @@
     <row r="113" ht="66" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>RiskDecision</t>
+          <t>ServiceLevelObjective</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -16931,17 +16931,17 @@
     <row r="114" ht="66" customHeight="1">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>AbuseCounter</t>
+          <t>ErrorBudget</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>平台全局/Identity abuse domain</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -16958,22 +16958,22 @@
     <row r="115" ht="66" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -16985,22 +16985,22 @@
     <row r="116" ht="66" customHeight="1">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>RiskCase</t>
+          <t>OnCallRoute</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -17012,12 +17012,12 @@
     <row r="117" ht="66" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>PRD-110</t>
+          <t>PRD-109</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>RiskAppeal</t>
+          <t>TelemetryPolicy</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -17039,22 +17039,22 @@
     <row r="118" ht="66" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>PRD-111</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>RiskSignal</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -17066,22 +17066,22 @@
     <row r="119" ht="66" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>PRD-111</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>FailoverPlan</t>
+          <t>RiskDecision</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -17093,17 +17093,17 @@
     <row r="120" ht="66" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>PRD-111</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>DisasterRecoveryRun</t>
+          <t>AbuseCounter</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>平台全局/Identity abuse domain</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -17120,22 +17120,22 @@
     <row r="121" ht="66" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>PRD-111</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>RecoveryPoint</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -17147,12 +17147,12 @@
     <row r="122" ht="66" customHeight="1">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>PRD-111</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>RestoreEvidence</t>
+          <t>RiskCase</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -17174,22 +17174,22 @@
     <row r="123" ht="66" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-110</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>StatusComponent</t>
+          <t>RiskAppeal</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -17201,12 +17201,12 @@
     <row r="124" ht="66" customHeight="1">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-111</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -17228,12 +17228,12 @@
     <row r="125" ht="66" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-111</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>IncidentUpdate</t>
+          <t>FailoverPlan</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -17255,22 +17255,22 @@
     <row r="126" ht="66" customHeight="1">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-111</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>MaintenanceWindow</t>
+          <t>DisasterRecoveryRun</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -17282,22 +17282,22 @@
     <row r="127" ht="66" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-111</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>StatusSubscription</t>
+          <t>RecoveryPoint</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -17309,12 +17309,12 @@
     <row r="128" ht="66" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>PRD-112</t>
+          <t>PRD-111</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Postmortem</t>
+          <t>RestoreEvidence</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -17336,12 +17336,12 @@
     <row r="129" ht="66" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>PRD-113</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>CapacityForecast</t>
+          <t>StatusComponent</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -17363,22 +17363,22 @@
     <row r="130" ht="66" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>PRD-113</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>LoadTestRun</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -17390,22 +17390,22 @@
     <row r="131" ht="66" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>PRD-113</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ChaosExperiment</t>
+          <t>IncidentUpdate</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -17417,22 +17417,22 @@
     <row r="132" ht="66" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>PRD-113</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>PerformanceBaseline</t>
+          <t>MaintenanceWindow</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -17444,22 +17444,22 @@
     <row r="133" ht="66" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>PRD-113</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>PlatformCostAllocation</t>
+          <t>StatusSubscription</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -17471,22 +17471,22 @@
     <row r="134" ht="66" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>PRD-114</t>
+          <t>PRD-112</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>VerifiedDomain</t>
+          <t>Postmortem</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -17498,22 +17498,22 @@
     <row r="135" ht="66" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>PRD-114</t>
+          <t>PRD-113</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>SsoConnection</t>
+          <t>CapacityForecast</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -17525,12 +17525,12 @@
     <row r="136" ht="66" customHeight="1">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>PRD-114</t>
+          <t>PRD-113</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>SsoCertificate</t>
+          <t>LoadTestRun</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -17552,12 +17552,12 @@
     <row r="137" ht="66" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>PRD-114</t>
+          <t>PRD-113</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>AccountFederationLink</t>
+          <t>ChaosExperiment</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -17579,22 +17579,22 @@
     <row r="138" ht="66" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>PRD-114</t>
+          <t>PRD-113</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>SsoPolicy</t>
+          <t>PerformanceBaseline</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -17606,22 +17606,22 @@
     <row r="139" ht="66" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-113</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>ScimToken</t>
+          <t>PlatformCostAllocation</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -17633,22 +17633,22 @@
     <row r="140" ht="66" customHeight="1">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-114</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ScimUserLink</t>
+          <t>VerifiedDomain</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -17660,12 +17660,12 @@
     <row r="141" ht="66" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-114</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>ScimGroupLink</t>
+          <t>SsoConnection</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -17687,12 +17687,12 @@
     <row r="142" ht="66" customHeight="1">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-114</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ScimRoleMapping</t>
+          <t>SsoCertificate</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -17714,12 +17714,12 @@
     <row r="143" ht="66" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-114</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>ScimSyncRun</t>
+          <t>AccountFederationLink</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -17741,12 +17741,12 @@
     <row r="144" ht="66" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>PRD-115</t>
+          <t>PRD-114</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ScimConflict</t>
+          <t>SsoPolicy</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -17768,12 +17768,12 @@
     <row r="145" ht="66" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>MfaEnrollment</t>
+          <t>ScimToken</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -17795,12 +17795,12 @@
     <row r="146" ht="66" customHeight="1">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>WebAuthnCredential</t>
+          <t>ScimUserLink</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -17822,12 +17822,12 @@
     <row r="147" ht="66" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>RecoveryCodeSet</t>
+          <t>ScimGroupLink</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -17849,12 +17849,12 @@
     <row r="148" ht="66" customHeight="1">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>TrustedDevice</t>
+          <t>ScimRoleMapping</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -17876,12 +17876,12 @@
     <row r="149" ht="66" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>ConditionalAccessPolicy</t>
+          <t>ScimSyncRun</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -17903,12 +17903,12 @@
     <row r="150" ht="66" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>PRD-116</t>
+          <t>PRD-115</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>StepUpGrant</t>
+          <t>ScimConflict</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -17930,12 +17930,12 @@
     <row r="151" ht="66" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>DataClassification</t>
+          <t>MfaEnrollment</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -17957,12 +17957,12 @@
     <row r="152" ht="66" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ResidencyPolicy</t>
+          <t>WebAuthnCredential</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -17984,12 +17984,12 @@
     <row r="153" ht="66" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>RetentionPolicy</t>
+          <t>RecoveryCodeSet</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -18011,12 +18011,12 @@
     <row r="154" ht="66" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>LegalHold</t>
+          <t>TrustedDevice</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -18038,12 +18038,12 @@
     <row r="155" ht="66" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>DeletionSchedule</t>
+          <t>ConditionalAccessPolicy</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -18065,12 +18065,12 @@
     <row r="156" ht="66" customHeight="1">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>PRD-117</t>
+          <t>PRD-116</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ResidencyEvidence</t>
+          <t>StepUpGrant</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -18092,12 +18092,12 @@
     <row r="157" ht="66" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>PRD-118</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>ServiceAccount</t>
+          <t>DataClassification</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -18119,12 +18119,12 @@
     <row r="158" ht="66" customHeight="1">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>PRD-118</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>OAuthClient</t>
+          <t>ResidencyPolicy</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -18146,12 +18146,12 @@
     <row r="159" ht="66" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>PRD-118</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ClientCredential</t>
+          <t>RetentionPolicy</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -18173,12 +18173,12 @@
     <row r="160" ht="66" customHeight="1">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>PRD-118</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>AccessTokenGrant</t>
+          <t>LegalHold</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -18200,12 +18200,12 @@
     <row r="161" ht="66" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>PRD-118</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>MachineIdentityAudit</t>
+          <t>DeletionSchedule</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -18227,22 +18227,22 @@
     <row r="162" ht="66" customHeight="1">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>PRD-119</t>
+          <t>PRD-117</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ProviderCatalogEntry</t>
+          <t>ResidencyEvidence</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -18254,22 +18254,22 @@
     <row r="163" ht="66" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>PRD-119</t>
+          <t>PRD-118</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>ProviderCapability</t>
+          <t>ServiceAccount</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -18281,22 +18281,22 @@
     <row r="164" ht="66" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>PRD-119</t>
+          <t>PRD-118</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>RegionalEndpointTemplate</t>
+          <t>OAuthClient</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -18308,12 +18308,12 @@
     <row r="165" ht="66" customHeight="1">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>PRD-119</t>
+          <t>PRD-118</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>ProviderPreflightRun</t>
+          <t>ClientCredential</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -18335,12 +18335,12 @@
     <row r="166" ht="66" customHeight="1">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>PRD-119</t>
+          <t>PRD-118</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>CompatibilityProfile</t>
+          <t>AccessTokenGrant</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -18362,12 +18362,12 @@
     <row r="167" ht="66" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>PRD-120</t>
+          <t>PRD-118</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>EdgeDeployment</t>
+          <t>MachineIdentityAudit</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -18389,22 +18389,22 @@
     <row r="168" ht="66" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>PRD-120</t>
+          <t>PRD-119</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>EdgeRegistrationIntent</t>
+          <t>ProviderCatalogEntry</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -18416,22 +18416,22 @@
     <row r="169" ht="66" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>PRD-120</t>
+          <t>PRD-119</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>DeviceIdentity</t>
+          <t>ProviderCapability</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -18443,22 +18443,22 @@
     <row r="170" ht="66" customHeight="1">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>PRD-120</t>
+          <t>PRD-119</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>DeviceCertificate</t>
+          <t>RegionalEndpointTemplate</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -18470,12 +18470,12 @@
     <row r="171" ht="66" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>PRD-120</t>
+          <t>PRD-119</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>EdgeSession</t>
+          <t>ProviderPreflightRun</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -18497,12 +18497,12 @@
     <row r="172" ht="66" customHeight="1">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-119</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>DesiredState</t>
+          <t>CompatibilityProfile</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -18524,12 +18524,12 @@
     <row r="173" ht="66" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-120</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>SignedSnapshot</t>
+          <t>EdgeDeployment</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -18551,12 +18551,12 @@
     <row r="174" ht="66" customHeight="1">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-120</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>SnapshotArtifact</t>
+          <t>EdgeRegistrationIntent</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -18578,12 +18578,12 @@
     <row r="175" ht="66" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-120</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>ApplyAttempt</t>
+          <t>DeviceIdentity</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -18605,12 +18605,12 @@
     <row r="176" ht="66" customHeight="1">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-120</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>EdgeAck</t>
+          <t>DeviceCertificate</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -18632,12 +18632,12 @@
     <row r="177" ht="66" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>PRD-121</t>
+          <t>PRD-120</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>LastKnownGood</t>
+          <t>EdgeSession</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -18659,12 +18659,12 @@
     <row r="178" ht="66" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>PRD-122</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>TelemetryPolicy</t>
+          <t>DesiredState</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -18686,12 +18686,12 @@
     <row r="179" ht="66" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>PRD-122</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>TelemetryBatch</t>
+          <t>SignedSnapshot</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -18713,12 +18713,12 @@
     <row r="180" ht="66" customHeight="1">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>PRD-122</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>UsageSyncCursor</t>
+          <t>SnapshotArtifact</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -18740,12 +18740,12 @@
     <row r="181" ht="66" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>PRD-122</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>EdgeFailureSummary</t>
+          <t>ApplyAttempt</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -18767,12 +18767,12 @@
     <row r="182" ht="66" customHeight="1">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>PRD-122</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>TelemetryReceipt</t>
+          <t>EdgeAck</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -18794,12 +18794,12 @@
     <row r="183" ht="66" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>PRD-123</t>
+          <t>PRD-121</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>LocalSecret</t>
+          <t>LastKnownGood</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18821,12 +18821,12 @@
     <row r="184" ht="66" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>PRD-123</t>
+          <t>PRD-122</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>SecretReference</t>
+          <t>TelemetryPolicy</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18848,12 +18848,12 @@
     <row r="185" ht="66" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>PRD-123</t>
+          <t>PRD-122</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>SecretVersion</t>
+          <t>TelemetryBatch</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18875,12 +18875,12 @@
     <row r="186" ht="66" customHeight="1">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>PRD-123</t>
+          <t>PRD-122</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>SecretRotation</t>
+          <t>UsageSyncCursor</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18902,12 +18902,12 @@
     <row r="187" ht="66" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>PRD-123</t>
+          <t>PRD-122</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>ProviderConnectionTest</t>
+          <t>EdgeFailureSummary</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18929,12 +18929,12 @@
     <row r="188" ht="66" customHeight="1">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>PRD-124</t>
+          <t>PRD-122</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>InstallerRelease</t>
+          <t>TelemetryReceipt</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18956,12 +18956,12 @@
     <row r="189" ht="66" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>PRD-124</t>
+          <t>PRD-123</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>InstallProfile</t>
+          <t>LocalSecret</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18983,12 +18983,12 @@
     <row r="190" ht="66" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>PRD-124</t>
+          <t>PRD-123</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>PreflightReport</t>
+          <t>SecretReference</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -19010,12 +19010,12 @@
     <row r="191" ht="66" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>PRD-124</t>
+          <t>PRD-123</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Installation</t>
+          <t>SecretVersion</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -19037,12 +19037,12 @@
     <row r="192" ht="66" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>PRD-124</t>
+          <t>PRD-123</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>InstallAudit</t>
+          <t>SecretRotation</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -19064,12 +19064,12 @@
     <row r="193" ht="66" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>PRD-125</t>
+          <t>PRD-123</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>DeploymentValidation</t>
+          <t>ProviderConnectionTest</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -19091,12 +19091,12 @@
     <row r="194" ht="66" customHeight="1">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>PRD-125</t>
+          <t>PRD-124</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>ValidationCheck</t>
+          <t>InstallerRelease</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -19118,12 +19118,12 @@
     <row r="195" ht="66" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>PRD-125</t>
+          <t>PRD-124</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>SupportBundle</t>
+          <t>InstallProfile</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -19145,12 +19145,12 @@
     <row r="196" ht="66" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>PRD-125</t>
+          <t>PRD-124</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>DeliveryAcceptance</t>
+          <t>PreflightReport</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -19172,12 +19172,12 @@
     <row r="197" ht="66" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>PRD-126</t>
+          <t>PRD-124</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>FleetDeployment</t>
+          <t>Installation</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -19199,12 +19199,12 @@
     <row r="198" ht="66" customHeight="1">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>PRD-126</t>
+          <t>PRD-124</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>EdgeHealthSnapshot</t>
+          <t>InstallAudit</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -19226,12 +19226,12 @@
     <row r="199" ht="66" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>PRD-126</t>
+          <t>PRD-125</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>DiagnosticGrant</t>
+          <t>DeploymentValidation</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -19253,12 +19253,12 @@
     <row r="200" ht="66" customHeight="1">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>PRD-126</t>
+          <t>PRD-125</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>DiagnosticCommand</t>
+          <t>ValidationCheck</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -19280,12 +19280,12 @@
     <row r="201" ht="66" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>PRD-126</t>
+          <t>PRD-125</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>DiagnosticResult</t>
+          <t>SupportBundle</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -19307,22 +19307,22 @@
     <row r="202" ht="66" customHeight="1">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-125</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>GatewayRelease</t>
+          <t>DeliveryAcceptance</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -19334,12 +19334,12 @@
     <row r="203" ht="66" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-126</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>ReleaseArtifact</t>
+          <t>FleetDeployment</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -19361,12 +19361,12 @@
     <row r="204" ht="66" customHeight="1">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-126</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>ReleaseChannel</t>
+          <t>EdgeHealthSnapshot</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -19388,12 +19388,12 @@
     <row r="205" ht="66" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-126</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Rollout</t>
+          <t>DiagnosticGrant</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -19415,12 +19415,12 @@
     <row r="206" ht="66" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-126</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>RolloutBatch</t>
+          <t>DiagnosticCommand</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -19442,12 +19442,12 @@
     <row r="207" ht="66" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>PRD-127</t>
+          <t>PRD-126</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>MaintenanceWindow</t>
+          <t>DiagnosticResult</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -19474,17 +19474,17 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>RollbackAttempt</t>
+          <t>GatewayRelease</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -19496,12 +19496,12 @@
     <row r="209" ht="66" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>PRD-128</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>EdgeLicense</t>
+          <t>ReleaseArtifact</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -19523,12 +19523,12 @@
     <row r="210" ht="66" customHeight="1">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>PRD-128</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>SignedEntitlement</t>
+          <t>ReleaseChannel</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -19550,12 +19550,12 @@
     <row r="211" ht="66" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>PRD-128</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>CapacityGrant</t>
+          <t>Rollout</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -19577,12 +19577,12 @@
     <row r="212" ht="66" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>PRD-128</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>LicenseLease</t>
+          <t>RolloutBatch</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -19604,12 +19604,12 @@
     <row r="213" ht="66" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>PRD-128</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>LicenseAudit</t>
+          <t>MaintenanceWindow</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -19631,12 +19631,12 @@
     <row r="214" ht="66" customHeight="1">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-127</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>EdgeBackup</t>
+          <t>RollbackAttempt</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -19658,12 +19658,12 @@
     <row r="215" ht="66" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-128</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>BackupChunk</t>
+          <t>EdgeLicense</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -19685,12 +19685,12 @@
     <row r="216" ht="66" customHeight="1">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-128</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>BackupKeyEnvelope</t>
+          <t>SignedEntitlement</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -19712,12 +19712,12 @@
     <row r="217" ht="66" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-128</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>RestoreJob</t>
+          <t>CapacityGrant</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -19739,12 +19739,12 @@
     <row r="218" ht="66" customHeight="1">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-128</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>RestoreVerification</t>
+          <t>LicenseLease</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -19766,12 +19766,12 @@
     <row r="219" ht="66" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>PRD-129</t>
+          <t>PRD-128</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>PrivateDrDrill</t>
+          <t>LicenseAudit</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -19793,12 +19793,12 @@
     <row r="220" ht="66" customHeight="1">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>PRD-130</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>OfflineBundle</t>
+          <t>EdgeBackup</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -19820,12 +19820,12 @@
     <row r="221" ht="66" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>PRD-130</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>BundleManifest</t>
+          <t>BackupChunk</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -19847,12 +19847,12 @@
     <row r="222" ht="66" customHeight="1">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>PRD-130</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>BundleTransfer</t>
+          <t>BackupKeyEnvelope</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -19874,12 +19874,12 @@
     <row r="223" ht="66" customHeight="1">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>PRD-130</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>OfflineSyncCursor</t>
+          <t>RestoreJob</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -19901,12 +19901,12 @@
     <row r="224" ht="66" customHeight="1">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>PRD-130</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>OfflineConflict</t>
+          <t>RestoreVerification</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -19928,12 +19928,12 @@
     <row r="225" ht="66" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-129</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>MigrationAssessment</t>
+          <t>PrivateDrDrill</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -19955,12 +19955,12 @@
     <row r="226" ht="66" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-130</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>MigrationPlan</t>
+          <t>OfflineBundle</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -19982,12 +19982,12 @@
     <row r="227" ht="66" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-130</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MigrationRun</t>
+          <t>BundleManifest</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -20009,12 +20009,12 @@
     <row r="228" ht="66" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-130</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MigrationDifference</t>
+          <t>BundleTransfer</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -20036,12 +20036,12 @@
     <row r="229" ht="66" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-130</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>CutoverCheckpoint</t>
+          <t>OfflineSyncCursor</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -20063,12 +20063,12 @@
     <row r="230" ht="66" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>PRD-131</t>
+          <t>PRD-130</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>RollbackPlan</t>
+          <t>OfflineConflict</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -20090,12 +20090,12 @@
     <row r="231" ht="66" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SupportTicket</t>
+          <t>MigrationAssessment</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -20117,12 +20117,12 @@
     <row r="232" ht="66" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>TicketMessage</t>
+          <t>MigrationPlan</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -20144,12 +20144,12 @@
     <row r="233" ht="66" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>TicketAttachment</t>
+          <t>MigrationRun</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -20171,12 +20171,12 @@
     <row r="234" ht="66" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>SlaClock</t>
+          <t>MigrationDifference</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -20198,12 +20198,12 @@
     <row r="235" ht="66" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Escalation</t>
+          <t>CutoverCheckpoint</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -20225,12 +20225,12 @@
     <row r="236" ht="66" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>PRD-132</t>
+          <t>PRD-131</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>SatisfactionSurvey</t>
+          <t>RollbackPlan</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -20252,22 +20252,22 @@
     <row r="237" ht="66" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>PRD-133</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>ApiVersion</t>
+          <t>SupportTicket</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -20279,22 +20279,22 @@
     <row r="238" ht="66" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>PRD-133</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>ApiContractSnapshot</t>
+          <t>TicketMessage</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -20306,22 +20306,22 @@
     <row r="239" ht="66" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>PRD-133</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>SdkRelease</t>
+          <t>TicketAttachment</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
@@ -20333,22 +20333,22 @@
     <row r="240" ht="66" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>PRD-133</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>DeprecationNotice</t>
+          <t>SlaClock</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
@@ -20360,22 +20360,22 @@
     <row r="241" ht="66" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>PRD-133</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>WebhookSchemaVersion</t>
+          <t>Escalation</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
@@ -20387,22 +20387,22 @@
     <row r="242" ht="66" customHeight="1">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-132</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>ConsentRecord</t>
+          <t>SatisfactionSurvey</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -20414,22 +20414,22 @@
     <row r="243" ht="66" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-133</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>PrivacyPreference</t>
+          <t>ApiVersion</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
@@ -20441,22 +20441,22 @@
     <row r="244" ht="66" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-133</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>DataSubjectRequest</t>
+          <t>ApiContractSnapshot</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -20468,22 +20468,22 @@
     <row r="245" ht="66" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-133</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>IdentityExport</t>
+          <t>SdkRelease</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -20495,22 +20495,22 @@
     <row r="246" ht="66" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-133</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>ErasureDecision</t>
+          <t>DeprecationNotice</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -20522,22 +20522,22 @@
     <row r="247" ht="66" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>PRD-134</t>
+          <t>PRD-133</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>RetentionException</t>
+          <t>WebhookSchemaVersion</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
@@ -20549,12 +20549,12 @@
     <row r="248" ht="66" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>ComplianceControl</t>
+          <t>ConsentRecord</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -20576,22 +20576,22 @@
     <row r="249" ht="66" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>ControlMapping</t>
+          <t>PrivacyPreference</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
@@ -20603,12 +20603,12 @@
     <row r="250" ht="66" customHeight="1">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>ComplianceEvidence</t>
+          <t>DataSubjectRequest</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -20630,12 +20630,12 @@
     <row r="251" ht="66" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>ComplianceException</t>
+          <t>IdentityExport</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -20657,12 +20657,12 @@
     <row r="252" ht="66" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>RemediationTask</t>
+          <t>ErasureDecision</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -20684,12 +20684,12 @@
     <row r="253" ht="66" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>PRD-135</t>
+          <t>PRD-134</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>ComplianceReport</t>
+          <t>RetentionException</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -20711,12 +20711,12 @@
     <row r="254" ht="66" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>SbomReport</t>
+          <t>ComplianceControl</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -20738,12 +20738,12 @@
     <row r="255" ht="66" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>ArtifactSignature</t>
+          <t>ControlMapping</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -20765,22 +20765,22 @@
     <row r="256" ht="66" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>BuildProvenance</t>
+          <t>ComplianceEvidence</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
@@ -20792,22 +20792,22 @@
     <row r="257" ht="66" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>VulnerabilityFinding</t>
+          <t>ComplianceException</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
@@ -20819,12 +20819,12 @@
     <row r="258" ht="66" customHeight="1">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>SecurityException</t>
+          <t>RemediationTask</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -20846,12 +20846,12 @@
     <row r="259" ht="66" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>PRD-136</t>
+          <t>PRD-135</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>PatchRelease</t>
+          <t>ComplianceReport</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -20873,22 +20873,22 @@
     <row r="260" ht="66" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>PRD-137</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>SecurityAssessment</t>
+          <t>SbomReport</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -20900,22 +20900,22 @@
     <row r="261" ht="66" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>PRD-137</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>IsolationTestRun</t>
+          <t>ArtifactSignature</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -20927,22 +20927,22 @@
     <row r="262" ht="66" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>PRD-137</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>PenTestFinding</t>
+          <t>BuildProvenance</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -20954,22 +20954,22 @@
     <row r="263" ht="66" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>PRD-137</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Remediation</t>
+          <t>VulnerabilityFinding</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -20981,12 +20981,12 @@
     <row r="264" ht="66" customHeight="1">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>PRD-137</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>RiskAcceptance</t>
+          <t>SecurityException</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -21008,22 +21008,22 @@
     <row r="265" ht="66" customHeight="1">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-136</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>LaunchGate</t>
+          <t>PatchRelease</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -21035,12 +21035,12 @@
     <row r="266" ht="66" customHeight="1">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-137</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>LaunchEvidence</t>
+          <t>SecurityAssessment</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -21062,22 +21062,22 @@
     <row r="267" ht="66" customHeight="1">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-137</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>LaunchWave</t>
+          <t>IsolationTestRun</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -21089,22 +21089,22 @@
     <row r="268" ht="66" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-137</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>GoNoGoDecision</t>
+          <t>PenTestFinding</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -21116,12 +21116,12 @@
     <row r="269" ht="66" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-137</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>LaunchRollback</t>
+          <t>Remediation</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -21143,12 +21143,12 @@
     <row r="270" ht="66" customHeight="1">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>PRD-138</t>
+          <t>PRD-137</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>PostLaunchReview</t>
+          <t>RiskAcceptance</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -21170,22 +21170,22 @@
     <row r="271" ht="66" customHeight="1">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>ChannelPartner</t>
+          <t>LaunchGate</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
@@ -21197,12 +21197,12 @@
     <row r="272" ht="66" customHeight="1">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>ChannelMembership</t>
+          <t>LaunchEvidence</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -21224,22 +21224,22 @@
     <row r="273" ht="66" customHeight="1">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>ReferralCode</t>
+          <t>LaunchWave</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -21251,22 +21251,22 @@
     <row r="274" ht="66" customHeight="1">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>RegisteredLead</t>
+          <t>GoNoGoDecision</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -21278,12 +21278,12 @@
     <row r="275" ht="66" customHeight="1">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceAttribution</t>
+          <t>LaunchRollback</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -21305,12 +21305,12 @@
     <row r="276" ht="66" customHeight="1">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>PRD-139</t>
+          <t>PRD-138</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>AttributionChange</t>
+          <t>PostLaunchReview</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>CommissionRule</t>
+          <t>ChannelPartner</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>ChannelStatement</t>
+          <t>ChannelMembership</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -21386,12 +21386,12 @@
     <row r="279" ht="66" customHeight="1">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>CustomerAccountProjection</t>
+          <t>ReferralCode</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -21413,12 +21413,12 @@
     <row r="280" ht="66" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>CustomerContact</t>
+          <t>RegisteredLead</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -21440,12 +21440,12 @@
     <row r="281" ht="66" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>CustomerHealthSnapshot</t>
+          <t>WorkspaceAttribution</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
@@ -21467,12 +21467,12 @@
     <row r="282" ht="66" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>SuccessPlan</t>
+          <t>AttributionChange</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -21494,12 +21494,12 @@
     <row r="283" ht="66" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>CustomerTask</t>
+          <t>CommissionRule</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
@@ -21521,12 +21521,12 @@
     <row r="284" ht="66" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>PRD-140</t>
+          <t>PRD-139</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>RenewalOpportunity</t>
+          <t>ChannelStatement</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>QbrSummary</t>
+          <t>CustomerAccountProjection</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -21575,12 +21575,12 @@
     <row r="286" ht="66" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>AcquisitionSource</t>
+          <t>CustomerContact</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -21602,12 +21602,12 @@
     <row r="287" ht="66" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>GrowthFunnelSnapshot</t>
+          <t>CustomerHealthSnapshot</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -21629,12 +21629,12 @@
     <row r="288" ht="66" customHeight="1">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>CohortSnapshot</t>
+          <t>SuccessPlan</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -21656,12 +21656,12 @@
     <row r="289" ht="66" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>CustomerTask</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
@@ -21683,12 +21683,12 @@
     <row r="290" ht="66" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>GrowthExperiment</t>
+          <t>RenewalOpportunity</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -21710,12 +21710,12 @@
     <row r="291" ht="66" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>PRD-141</t>
+          <t>PRD-140</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>ConversionAttribution</t>
+          <t>QbrSummary</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -21742,7 +21742,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>GrowthExport</t>
+          <t>AcquisitionSource</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -21764,22 +21764,22 @@
     <row r="293" ht="66" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>PlatformBrand</t>
+          <t>GrowthFunnelSnapshot</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
@@ -21791,22 +21791,22 @@
     <row r="294" ht="66" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>ChannelBrand</t>
+          <t>CohortSnapshot</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -21818,12 +21818,12 @@
     <row r="295" ht="66" customHeight="1">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>DeploymentBrand</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -21845,22 +21845,22 @@
     <row r="296" ht="66" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>VerifiedDomain</t>
+          <t>GrowthExperiment</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
@@ -21872,12 +21872,12 @@
     <row r="297" ht="66" customHeight="1">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>BrandAsset</t>
+          <t>ConversionAttribution</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -21899,22 +21899,22 @@
     <row r="298" ht="66" customHeight="1">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>PRD-142</t>
+          <t>PRD-141</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>BrandMigrationCursor</t>
+          <t>GrowthExport</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -21926,12 +21926,12 @@
     <row r="299" ht="66" customHeight="1">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>PRD-143</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>ProviderAdapterRelease</t>
+          <t>PlatformBrand</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
@@ -21953,12 +21953,12 @@
     <row r="300" ht="66" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>PRD-143</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>AdapterContractRunProjection</t>
+          <t>ChannelBrand</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -21980,22 +21980,22 @@
     <row r="301" ht="66" customHeight="1">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>PRD-143</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>BuiltinErrorCatalog</t>
+          <t>DeploymentBrand</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -22007,22 +22007,22 @@
     <row r="302" ht="66" customHeight="1">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>PRD-143</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceErrorOverride</t>
+          <t>VerifiedDomain</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
@@ -22034,22 +22034,22 @@
     <row r="303" ht="66" customHeight="1">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>PRD-143</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>ProviderCompatibilityProjection</t>
+          <t>BrandAsset</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
@@ -22061,12 +22061,12 @@
     <row r="304" ht="66" customHeight="1">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-142</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>PlatformPlanCatalog</t>
+          <t>BrandMigrationCursor</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
@@ -22088,22 +22088,22 @@
     <row r="305" ht="66" customHeight="1">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-143</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceSubscriptionProjection</t>
+          <t>ProviderAdapterRelease</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
@@ -22115,12 +22115,12 @@
     <row r="306" ht="66" customHeight="1">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-143</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>PlatformInvoice</t>
+          <t>AdapterContractRunProjection</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -22142,22 +22142,22 @@
     <row r="307" ht="66" customHeight="1">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-143</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>BillingDisputeCase</t>
+          <t>BuiltinErrorCatalog</t>
         </is>
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E307" s="3" t="inlineStr">
@@ -22169,12 +22169,12 @@
     <row r="308" ht="66" customHeight="1">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-143</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>ProviderCostRate</t>
+          <t>WorkspaceErrorOverride</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -22196,22 +22196,22 @@
     <row r="309" ht="66" customHeight="1">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>PRD-144</t>
+          <t>PRD-143</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>InternalFinOpsLedger</t>
+          <t>ProviderCompatibilityProjection</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>BillingDomainReconciliation</t>
+          <t>PlatformPlanCatalog</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -22250,22 +22250,22 @@
     <row r="311" ht="66" customHeight="1">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>PlatformDashboardProjection</t>
+          <t>WorkspaceSubscriptionProjection</t>
         </is>
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
@@ -22277,22 +22277,22 @@
     <row r="312" ht="66" customHeight="1">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceDashboardProjection</t>
+          <t>PlatformInvoice</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -22304,12 +22304,12 @@
     <row r="313" ht="66" customHeight="1">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>DomainApprovalQueue</t>
+          <t>BillingDisputeCase</t>
         </is>
       </c>
       <c r="C313" s="3" t="inlineStr">
@@ -22331,12 +22331,12 @@
     <row r="314" ht="66" customHeight="1">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>AssistantQueryProjection</t>
+          <t>ProviderCostRate</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
@@ -22358,22 +22358,22 @@
     <row r="315" ht="66" customHeight="1">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>AccountPreference</t>
+          <t>InternalFinOpsLedger</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E315" s="3" t="inlineStr">
@@ -22385,22 +22385,22 @@
     <row r="316" ht="66" customHeight="1">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>PRD-145</t>
+          <t>PRD-144</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>DeploymentDiagnosticProjection</t>
+          <t>BillingDomainReconciliation</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
@@ -22412,22 +22412,22 @@
     <row r="317" ht="66" customHeight="1">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>PRD-146</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>WorkspaceNavigationProjection</t>
+          <t>PlatformDashboardProjection</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -22439,12 +22439,12 @@
     <row r="318" ht="66" customHeight="1">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>PRD-146</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>RoleTaskHome</t>
+          <t>WorkspaceDashboardProjection</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -22466,12 +22466,12 @@
     <row r="319" ht="66" customHeight="1">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>PRD-146</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>NavigationPreference</t>
+          <t>DomainApprovalQueue</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
@@ -22493,12 +22493,12 @@
     <row r="320" ht="66" customHeight="1">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>PRD-146</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>AdvancedToolEntitlement</t>
+          <t>AssistantQueryProjection</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -22520,22 +22520,22 @@
     <row r="321" ht="66" customHeight="1">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>PRD-146</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>NavigationContractSnapshot</t>
+          <t>AccountPreference</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>Workspace/租户</t>
+          <t>平台全局</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -22547,12 +22547,12 @@
     <row r="322" ht="66" customHeight="1">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>PRD-147</t>
+          <t>PRD-145</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>ConsoleDomainMigration</t>
+          <t>DeploymentDiagnosticProjection</t>
         </is>
       </c>
       <c r="C322" s="3" t="inlineStr">
@@ -22574,12 +22574,12 @@
     <row r="323" ht="66" customHeight="1">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>PRD-147</t>
+          <t>PRD-146</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>ConsoleBackfillCursor</t>
+          <t>WorkspaceNavigationProjection</t>
         </is>
       </c>
       <c r="C323" s="3" t="inlineStr">
@@ -22601,12 +22601,12 @@
     <row r="324" ht="66" customHeight="1">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>PRD-147</t>
+          <t>PRD-146</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>LegacyRouteTombstone</t>
+          <t>RoleTaskHome</t>
         </is>
       </c>
       <c r="C324" s="3" t="inlineStr">
@@ -22628,12 +22628,12 @@
     <row r="325" ht="66" customHeight="1">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>PRD-147</t>
+          <t>PRD-146</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>NavigationContractSnapshot</t>
+          <t>NavigationPreference</t>
         </is>
       </c>
       <c r="C325" s="3" t="inlineStr">
@@ -22655,12 +22655,12 @@
     <row r="326" ht="66" customHeight="1">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>PRD-147</t>
+          <t>PRD-146</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>DomainReconciliation</t>
+          <t>AdvancedToolEntitlement</t>
         </is>
       </c>
       <c r="C326" s="3" t="inlineStr">
@@ -22682,22 +22682,22 @@
     <row r="327" ht="66" customHeight="1">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>PRD-148</t>
+          <t>PRD-146</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>GaGate</t>
+          <t>NavigationContractSnapshot</t>
         </is>
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
@@ -22709,22 +22709,22 @@
     <row r="328" ht="66" customHeight="1">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>PRD-148</t>
+          <t>PRD-147</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>GaEvidence</t>
+          <t>ConsoleDomainMigration</t>
         </is>
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -22736,22 +22736,22 @@
     <row r="329" ht="66" customHeight="1">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>PRD-148</t>
+          <t>PRD-147</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>GaDecision</t>
+          <t>ConsoleBackfillCursor</t>
         </is>
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
@@ -22763,22 +22763,22 @@
     <row r="330" ht="66" customHeight="1">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>PRD-148</t>
+          <t>PRD-147</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>GaLaunch</t>
+          <t>LegacyRouteTombstone</t>
         </is>
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -22790,22 +22790,22 @@
     <row r="331" ht="66" customHeight="1">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>PRD-148</t>
+          <t>PRD-147</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>GaRollback</t>
+          <t>NavigationContractSnapshot</t>
         </is>
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>平台全局</t>
+          <t>Workspace/租户</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
         </is>
       </c>
       <c r="E331" s="3" t="inlineStr">
@@ -22817,32 +22817,194 @@
     <row r="332" ht="66" customHeight="1">
       <c r="A332" s="3" t="inlineStr">
         <is>
+          <t>PRD-147</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>DomainReconciliation</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t>Workspace/租户</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>必须带workspace_id/tenant_id并以复合外键绑定owner</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="66" customHeight="1">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
           <t>PRD-148</t>
         </is>
       </c>
-      <c r="B332" s="3" t="inlineStr">
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>GaGate</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>平台全局</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="66" customHeight="1">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>PRD-148</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>GaEvidence</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>平台全局</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="66" customHeight="1">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>PRD-148</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>GaDecision</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>平台全局</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="66" customHeight="1">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>PRD-148</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>GaLaunch</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>平台全局</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="66" customHeight="1">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>PRD-148</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>GaRollback</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>平台全局</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="66" customHeight="1">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>PRD-148</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
         <is>
           <t>PostGaReview</t>
         </is>
       </c>
-      <c r="C332" s="3" t="inlineStr">
+      <c r="C338" s="3" t="inlineStr">
         <is>
           <t>平台全局</t>
         </is>
       </c>
-      <c r="D332" s="3" t="inlineStr">
+      <c r="D338" s="3" t="inlineStr">
         <is>
           <t>全局对象不带tenant_id；通过受控关联引用Workspace</t>
         </is>
       </c>
-      <c r="E332" s="3" t="inlineStr">
+      <c r="E338" s="3" t="inlineStr">
         <is>
           <t>版本化/状态机/CAS；删除或停用保留审计事实；公开DTO使用字段白名单</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E332"/>
+  <autoFilter ref="A1:E338"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23591,7 +23753,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>personal Workspace的owner仅本人；organization Workspace的owner可维护本企业；platform_ops只看脱敏生命周期</t>
+          <t>GlobalSession只允许已验证账号创建空间；personal/organization Workspace的owner仅本人可读写；本条不授予平台角色或其他成员权限</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -23623,7 +23785,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>personal Workspace的owner仅本人；organization Workspace的owner可维护本企业；platform_ops只看脱敏生命周期</t>
+          <t>GlobalSession只允许已验证账号创建空间；personal/organization Workspace的owner仅本人可读写；本条不授予平台角色或其他成员权限</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -23655,7 +23817,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>personal Workspace的owner仅本人；organization Workspace的owner可维护本企业；platform_ops只看脱敏生命周期</t>
+          <t>GlobalSession只允许已验证账号创建空间；personal/organization Workspace的owner仅本人可读写；本条不授予平台角色或其他成员权限</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -23687,7 +23849,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>personal Workspace的owner仅本人；organization Workspace的owner可维护本企业；platform_ops只看脱敏生命周期</t>
+          <t>GlobalSession只允许已验证账号创建空间；personal/organization Workspace的owner仅本人可读写；本条不授予平台角色或其他成员权限</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -39543,7 +39705,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>跨租户/跨域/动态撤权/重放/SSRF/注入/敏感日志；专项：slug防枚举、企业名输出转义、Region不可静默跨境、Owner不可孤儿、创建幂等。</t>
+          <t>跨租户/跨域/动态撤权/重放/SSRF/注入/敏感日志；专项：GlobalSession与CSRF/Origin边界；Idempotency-Key只存HMAC并绑定规范body；slug冲突同形；企业名输出转义且不进日志/事件/幂等记录；Region允许列表失败关闭；Owner不可孤儿。</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..096已完成，下一项PRD-097。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..097已完成，下一项PRD-098。</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..097已完成，下一项PRD-098。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..114已完成，下一项PRD-115。</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..114已完成，下一项PRD-115。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..115已完成，下一项PRD-116。</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..115已完成，下一项PRD-116。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..116已完成，下一项PRD-117。</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -9235,7 +9235,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..116已完成，下一项PRD-117。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..119已完成，下一项PRD-120。</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_里程碑门禁'!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_风险与决策'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_角色页面矩阵'!$A$1:$F$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_现有导航处置'!$A$1:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_现有导航处置'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..119已完成，下一项PRD-120。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..120已完成，下一项PRD-121。</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>源码63项：44项企业Gateway保留，12项拆为独立平台/企业投影，5项完全迁入SaaS平台，1项迁到GlobalAccount壳层，1项退出登录后产品UI；不得只隐藏菜单，DOM、预取、API和数据owner必须同步切换。</t>
+          <t>源码64项：45项企业Gateway保留，12项拆为独立平台/企业投影，5项完全迁入SaaS平台，1项迁到GlobalAccount壳层，1项退出登录后产品UI；不得只隐藏菜单，DOM、预取、API和数据owner必须同步切换。</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2849,47 +2849,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>adapter-specs</t>
+          <t>private-gateways</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Adapter 规范</t>
+          <t>私有 Gateway</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>迁出企业</t>
+          <t>企业保留并归组</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>平台Provider工程台；企业Provider详情另建兼容摘要</t>
+          <t>客户自有Edge Deployment</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>owner/admin管理；developer/security_admin按权限只读</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>platform_provider_engineer/platform_security/release_manager</t>
+          <t>platform_ops只看独立Fleet脱敏投影</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>GET /adapter-specs；POST /internal/adapter-specs/{tenant_id}/activate；provider_adapter_catalog_activations</t>
+          <t>GET/POST /edge/deployments、/edge/registrations、/edge/deployments/{id}/revoke；edge_deployments及设备身份表</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>PRD-143/147</t>
+          <t>PRD-120..130/146</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>企业旧规范导航、DOM、预取和API归零；兼容摘要由Provider详情独立鉴权，不暴露内部schema、构建信息或发布权限</t>
+          <t>Workspace与Platform使用独立Session/API/DTO；注册材料、设备私钥、本地Secret和业务正文不得进入平台投影</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>adapter-contract-runs</t>
+          <t>adapter-specs</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CI 测试报告</t>
+          <t>Adapter 规范</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>平台Provider工程台</t>
+          <t>平台Provider工程台；企业Provider详情另建兼容摘要</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>GET /adapter-contract-runs及/{id}；POST /internal/tenants/{tenant_id}/adapter-contract-runs；runs/cases/outbox</t>
+          <t>GET /adapter-specs；POST /internal/adapter-specs/{tenant_id}/activate；provider_adapter_catalog_activations</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Runner、case详情和构建路径不进入企业DTO；企业兼容结论改在Provider详情提供；旧run/outbox水位保真</t>
+          <t>企业旧规范导航、DOM、预取和API归零；兼容摘要由Provider详情独立鉴权，不暴露内部schema、构建信息或发布权限</t>
         </is>
       </c>
     </row>
@@ -2953,47 +2953,47 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>provider-health</t>
+          <t>adapter-contract-runs</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Provider 状态</t>
+          <t>CI 测试报告</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分</t>
+          <t>迁出企业</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>本企业Provider健康；平台全局Provider/Cell健康</t>
+          <t>平台Provider工程台</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/security_admin/viewer按授权</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>platform_ops/platform_security/platform_support只读脱敏</t>
+          <t>platform_provider_engineer/platform_security/release_manager</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>GET /provider-health、POST /providers/{id}/probe；真实调用与探测事实</t>
+          <t>GET /adapter-contract-runs及/{id}；POST /internal/tenants/{tenant_id}/adapter-contract-runs；runs/cases/outbox</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>PRD-109/112/119/143/145</t>
+          <t>PRD-143/147</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>企业只见自身Endpoint/调用；平台聚合不得泄漏业务正文或Secret</t>
+          <t>Runner、case详情和构建路径不进入企业DTO；企业兼容结论改在Provider详情提供；旧run/outbox水位保真</t>
         </is>
       </c>
     </row>
@@ -3005,47 +3005,47 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>error-maps</t>
+          <t>provider-health</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>错误码管理</t>
+          <t>Provider 状态</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分并降级</t>
+          <t>平台/企业拆分</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>平台内置目录；企业受限覆盖</t>
+          <t>本企业Provider健康；平台全局Provider/Cell健康</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer高级入口</t>
+          <t>owner/admin/developer/security_admin/viewer按授权</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>platform_provider_engineer/platform_security/release_manager</t>
+          <t>platform_ops/platform_security/platform_support只读脱敏</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH /error-maps；builtin catalog、maps、versions、heads、events、facts</t>
+          <t>GET /provider-health、POST /providers/{id}/probe；真实调用与探测事实</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>PRD-143/147</t>
+          <t>PRD-109/112/119/143/145</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>企业不能改内置规则；覆盖只作用本Workspace且每个失败请求可解释追踪</t>
+          <t>企业只见自身Endpoint/调用；平台聚合不得泄漏业务正文或Secret</t>
         </is>
       </c>
     </row>
@@ -3057,47 +3057,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>error-maps</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>模型目录</t>
+          <t>错误码管理</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>平台/企业拆分并降级</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>企业可用模型</t>
+          <t>平台内置目录；企业受限覆盖</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer；viewer按授权只读</t>
+          <t>owner/admin/developer高级入口</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>平台Provider目录仅提供发布源</t>
+          <t>platform_provider_engineer/platform_security/release_manager</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH /models；模型owner保留tenant_id</t>
+          <t>GET/POST/PATCH /error-maps；builtin catalog、maps、versions、heads、events、facts</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>PRD-119/146</t>
+          <t>PRD-143/147</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>企业选择并治理自身可用模型；平台目录更新不能自动扩权</t>
+          <t>企业不能改内置规则；覆盖只作用本Workspace且每个失败请求可解释追踪</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>model-aliases</t>
+          <t>models</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>模型别名</t>
+          <t>模型目录</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3124,32 +3124,32 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>稳定业务模型别名</t>
+          <t>企业可用模型</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer按权限</t>
+          <t>owner/admin/developer；viewer按授权只读</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>平台Provider目录仅提供发布源</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>现有routing.read、model_aliases模块</t>
+          <t>GET/POST/PATCH /models；模型owner保留tenant_id</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>PRD-101/108/146</t>
+          <t>PRD-119/146</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>别名、环境和路由均绑定Workspace，切换可回滚</t>
+          <t>企业选择并治理自身可用模型；平台目录更新不能自动扩权</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>routing-policies</t>
+          <t>model-aliases</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>路由策略</t>
+          <t>模型别名</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>企业模型路由</t>
+          <t>稳定业务模型别名</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer按权限；auditor只读</t>
+          <t>owner/admin/developer按权限</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>现有routing.read及固定/成本/可用性路由</t>
+          <t>现有routing.read、model_aliases模块</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>后端准入与签名快照生效；前端隐藏不构成权限</t>
+          <t>别名、环境和路由均绑定Workspace，切换可回滚</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>model-quality-scores</t>
+          <t>routing-policies</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>模型评分</t>
+          <t>路由策略</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3228,32 +3228,32 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>企业模型质量与SLO</t>
+          <t>企业模型路由</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/viewer按授权</t>
+          <t>owner/admin/developer按权限；auditor只读</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>platform_ops只看平台运行聚合</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>现有model_quality.read、真实成功率/延迟与人工先验</t>
+          <t>现有routing.read及固定/成本/可用性路由</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>PRD-109/119/146</t>
+          <t>PRD-101/108/146</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>企业评分不成为平台客户健康或增长画像；聚合最小化</t>
+          <t>后端准入与签名快照生效；前端隐藏不构成权限</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>experiments</t>
+          <t>model-quality-scores</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>模型评测</t>
+          <t>模型评分</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3280,49 +3280,49 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>企业模型评测与A/B</t>
+          <t>企业模型质量与SLO</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer按权限；auditor只读</t>
+          <t>owner/admin/developer/viewer按授权</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_ops只看平台运行聚合</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>现有experiment.read及不可变实验配置/结果</t>
+          <t>现有model_quality.read、真实成功率/延迟与人工先验</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>PRD-101/106/146</t>
+          <t>PRD-109/119/146</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>分流、停止、用量和成本都绑定本Workspace并可审计</t>
+          <t>企业评分不成为平台客户健康或增长画像；聚合最小化</t>
         </is>
       </c>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>调用与成本</t>
+          <t>配置</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>experiments</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>项目与应用</t>
+          <t>模型评测</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>企业项目与应用</t>
+          <t>企业模型评测与A/B</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer；finance/security按范围只读</t>
+          <t>owner/admin/developer按权限；auditor只读</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>现有project.read；Project/Application为Key、日志、预算归属</t>
+          <t>现有experiment.read及不可变实验配置/结果</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>PRD-094/146</t>
+          <t>PRD-101/106/146</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>所有对象带tenant_id；职能角色只见授权项目</t>
+          <t>分流、停止、用量和成本都绑定本Workspace并可审计</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>virtual-keys</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Virtual Key</t>
+          <t>项目与应用</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>业务调用凭据</t>
+          <t>企业项目与应用</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer按权限</t>
+          <t>owner/admin/developer；finance/security按范围只读</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>platform_support与平台运营均不可读Secret</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>现有virtual_key.read及Key生命周期</t>
+          <t>现有project.read；Project/Application为Key、日志、预算归属</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>PRD-100/118/146</t>
+          <t>PRD-094/146</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>只显示一次的Secret不入日志；撤销、失败、用量和成本可追踪</t>
+          <t>所有对象带tenant_id；职能角色只见授权项目</t>
         </is>
       </c>
     </row>
@@ -3421,47 +3421,47 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>usage</t>
+          <t>virtual-keys</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>用量与成本</t>
+          <t>Virtual Key</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>企业保留；平台另建计量</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>企业技术用量与内部成本</t>
+          <t>业务调用凭据</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/finance_admin/auditor/viewer按字段</t>
+          <t>owner/admin/developer按权限</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>platform_billing只见平台商业计量</t>
+          <t>platform_support与平台运营均不可读Secret</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>GET /usage/*；Usage与价格快照</t>
+          <t>现有virtual_key.read及Key生命周期</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>PRD-099/122/144/146</t>
+          <t>PRD-100/118/146</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>平台计量与企业业务用量字段分域；成功失败取消重试均可追踪</t>
+          <t>只显示一次的Secret不入日志；撤销、失败、用量和成本可追踪</t>
         </is>
       </c>
     </row>
@@ -3473,47 +3473,47 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>finops-ledger</t>
+          <t>usage</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>FinOps 账本</t>
+          <t>用量与成本</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>企业保留；平台账本拆分</t>
+          <t>企业保留；平台另建计量</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>企业内部FinOps</t>
+          <t>企业技术用量与内部成本</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>owner/finance_admin；auditor只读</t>
+          <t>owner/admin/developer/finance_admin/auditor/viewer按字段</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>platform_billing仅平台商业账</t>
+          <t>platform_billing只见平台商业计量</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>GET/POST /finops/ledger；不可变分录与价格证据</t>
+          <t>GET /usage/*；Usage与价格快照</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>PRD-099/104/144/146</t>
+          <t>PRD-099/122/144/146</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>企业内部成本调整与平台收费分录不能互相写入或冒充</t>
+          <t>平台计量与企业业务用量字段分域；成功失败取消重试均可追踪</t>
         </is>
       </c>
     </row>
@@ -3525,47 +3525,47 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>model-prices</t>
+          <t>finops-ledger</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>模型价格</t>
+          <t>FinOps 账本</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分</t>
+          <t>企业保留；平台账本拆分</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>平台官方建议价；企业BYOK成本价</t>
+          <t>企业内部FinOps</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>owner/finance_admin；developer只读可用价格</t>
+          <t>owner/finance_admin；auditor只读</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>platform_billing/release_manager</t>
+          <t>platform_billing仅平台商业账</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>GET/POST /model-prices；历史/当前/未来价格与Usage快照</t>
+          <t>GET/POST /finops/ledger；不可变分录与价格证据</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>PRD-098/119/144/147</t>
+          <t>PRD-099/104/144/146</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>价格来源和版本明确；企业不能发布平台价，平台不能改企业私有成本</t>
+          <t>企业内部成本调整与平台收费分录不能互相写入或冒充</t>
         </is>
       </c>
     </row>
@@ -3577,47 +3577,47 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>response-cache</t>
+          <t>model-prices</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>响应缓存</t>
+          <t>模型价格</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>企业保留并入高级配置</t>
+          <t>平台/企业拆分</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>模型别名/路由详情的缓存策略</t>
+          <t>平台官方建议价；企业BYOK成本价</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/security_admin按权限</t>
+          <t>owner/finance_admin；developer只读可用价格</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_billing/release_manager</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>现有response_cache.read及按模型别名的可选能力</t>
+          <t>GET/POST /model-prices；历史/当前/未来价格与Usage快照</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>PRD-101/108/117/146</t>
+          <t>PRD-098/119/144/147</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；默认不缓存正文；租户、模型、保留和计费owner一致</t>
+          <t>价格来源和版本明确；企业不能发布平台价，平台不能改企业私有成本</t>
         </is>
       </c>
     </row>
@@ -3629,47 +3629,47 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>plans</t>
+          <t>response-cache</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>套餐管理</t>
+          <t>响应缓存</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分并改名</t>
+          <t>企业保留并入高级配置</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>平台套餐目录；企业订阅摘要</t>
+          <t>模型别名/路由详情的缓存策略</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>owner/finance_admin只读本Workspace订阅</t>
+          <t>owner/admin/developer/security_admin按权限</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>platform_owner/platform_billing</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>GET/PATCH /plans；plan/trial/quota事实</t>
+          <t>现有response_cache.read及按模型别名的可选能力</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>PRD-098/144/147</t>
+          <t>PRD-101/108/117/146</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>企业无套餐目录写入；Entitlement后端生效且回滚不扩大权益</t>
+          <t>不占普通一级导航；默认不缓存正文；租户、模型、保留和计费owner一致</t>
         </is>
       </c>
     </row>
@@ -3681,47 +3681,47 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>quota-buckets</t>
+          <t>plans</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>额度管理</t>
+          <t>套餐管理</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>企业保留；平台发放拆分</t>
+          <t>平台/企业拆分并改名</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>企业内部额度分配与消费</t>
+          <t>平台套餐目录；企业订阅摘要</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/finance_admin；developer只读自身</t>
+          <t>owner/finance_admin只读本Workspace订阅</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>platform_billing管理Entitlement上限而非企业分配</t>
+          <t>platform_owner/platform_billing</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>GET /quota-buckets；POST /quota-adjustments；四类额度及消费</t>
+          <t>GET/PATCH /plans；plan/trial/quota事实</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>PRD-098/099/144/146</t>
+          <t>PRD-098/144/147</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>平台权益上限和企业Project/Key额度分别授权、共同失败关闭</t>
+          <t>企业无套餐目录写入；Entitlement后端生效且回滚不扩大权益</t>
         </is>
       </c>
     </row>
@@ -3733,47 +3733,47 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>billing-disputes</t>
+          <t>quota-buckets</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>账单争议</t>
+          <t>额度管理</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分</t>
+          <t>企业保留；平台发放拆分</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>企业争议申请；平台争议裁决</t>
+          <t>企业内部额度分配与消费</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>owner/finance_admin提交和查看自身</t>
+          <t>owner/admin/finance_admin；developer只读自身</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>platform_billing裁决；platform_support协作但不裁决</t>
+          <t>platform_billing管理Entitlement上限而非企业分配</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH /billing-disputes；0073争议/调整状态机</t>
+          <t>GET /quota-buckets；POST /quota-adjustments；四类额度及消费</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>PRD-104/132/144/147</t>
+          <t>PRD-098/099/144/146</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>申请人不能裁决；金额调整不可变、双审批、统一审计和request_id</t>
+          <t>平台权益上限和企业Project/Key额度分别授权、共同失败关闭</t>
         </is>
       </c>
     </row>
@@ -3785,47 +3785,47 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>budgets</t>
+          <t>billing-disputes</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>预算中心</t>
+          <t>账单争议</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>平台/企业拆分</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>企业多级预算</t>
+          <t>企业争议申请；平台争议裁决</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/finance_admin；developer/auditor按范围只读</t>
+          <t>owner/finance_admin提交和查看自身</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_billing裁决；platform_support协作但不裁决</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>GET/POST/PATCH /budgets及/budget-status</t>
+          <t>GET/POST/PATCH /billing-disputes；0073争议/调整状态机</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>PRD-099/106/146</t>
+          <t>PRD-104/132/144/147</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>tenant/Project/Key预算后端准入；失败、阻断、审批和成本可追踪</t>
+          <t>申请人不能裁决；金额调整不可变、双审批、统一审计和request_id</t>
         </is>
       </c>
     </row>
@@ -3837,99 +3837,99 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>cost-anomalies</t>
+          <t>budgets</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>成本异常</t>
+          <t>预算中心</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>企业保留；平台另建商业异常</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>企业BYOK与内部成本异常</t>
+          <t>企业多级预算</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>owner/finance_admin/security_admin；auditor只读</t>
+          <t>owner/admin/finance_admin；developer/auditor按范围只读</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>platform_billing只看平台收费异常</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>GET/PATCH /cost-anomalies；runs/anomalies/actions/temporary overrides</t>
+          <t>GET/POST/PATCH /budgets及/budget-status</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>PRD-099/106/109/144/146</t>
+          <t>PRD-099/106/146</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>企业异常不泄漏到其他客户；平台异常不得获得Prompt/Response</t>
+          <t>tenant/Project/Key预算后端准入；失败、阻断、审批和成本可追踪</t>
         </is>
       </c>
     </row>
     <row r="35" ht="108" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>安全与治理</t>
+          <t>调用与成本</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>policies</t>
+          <t>cost-anomalies</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>策略管理</t>
+          <t>成本异常</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留；平台另建商业异常</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>企业治理策略</t>
+          <t>企业BYOK与内部成本异常</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin；developer/auditor只读授权范围</t>
+          <t>owner/finance_admin/security_admin；auditor只读</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_billing只看平台收费异常</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>现有policy.read及受限DSL</t>
+          <t>GET/PATCH /cost-anomalies；runs/anomalies/actions/temporary overrides</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/117/146</t>
+          <t>PRD-099/106/109/144/146</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>策略owner、版本、发布和回滚可审计；失效按安全类别失败关闭</t>
+          <t>企业异常不泄漏到其他客户；平台异常不得获得Prompt/Response</t>
         </is>
       </c>
     </row>
@@ -3941,27 +3941,27 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>policy-simulator</t>
+          <t>policies</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>策略模拟器</t>
+          <t>策略管理</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>企业保留并归高级工具</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>企业策略预演</t>
+          <t>企业治理策略</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin/developer按权限</t>
+          <t>owner/admin/security_admin；developer/auditor只读授权范围</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>现有policy.simulate；不调用真实Provider</t>
+          <t>现有policy.read及受限DSL</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/146</t>
+          <t>PRD-108/117/146</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>预演不能改变生产事实；输入正文不进入日志或验收证据</t>
+          <t>策略owner、版本、发布和回滚可审计；失效按安全类别失败关闭</t>
         </is>
       </c>
     </row>
@@ -3993,27 +3993,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>policy-snapshots</t>
+          <t>policy-simulator</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>策略发布</t>
+          <t>策略模拟器</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留并归高级工具</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>企业策略版本与回滚</t>
+          <t>企业策略预演</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin；auditor只读</t>
+          <t>owner/admin/security_admin/developer按权限</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4023,17 +4023,17 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>现有policy.read及不可变快照</t>
+          <t>现有policy.simulate；不调用真实Provider</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/121/146</t>
+          <t>PRD-108/146</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>签名、generation、LKG和动态撤权合同生效</t>
+          <t>预演不能改变生产事实；输入正文不进入日志或验收证据</t>
         </is>
       </c>
     </row>
@@ -4045,47 +4045,47 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>policy-templates</t>
+          <t>policy-snapshots</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>策略模板库</t>
+          <t>策略发布</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>平台模板目录；企业应用与覆盖</t>
+          <t>企业策略版本与回滚</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin应用；auditor只读</t>
+          <t>owner/admin/security_admin；auditor只读</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>platform_security/platform_compliance/release_manager发布</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>GET /policy-templates；POST /policy-templates/{policy_template_id}/apply；内置模板、适配和绑定事实</t>
+          <t>现有policy.read及不可变快照</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>PRD-117/119/143/146</t>
+          <t>PRD-108/121/146</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>企业不能篡改内置模板；套用产生tenant-scoped版本并可回滚</t>
+          <t>签名、generation、LKG和动态撤权合同生效</t>
         </is>
       </c>
     </row>
@@ -4097,47 +4097,47 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>dlp-rules</t>
+          <t>policy-templates</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>DLP 规则</t>
+          <t>策略模板库</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>平台/企业拆分</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>企业DLP</t>
+          <t>平台模板目录；企业应用与覆盖</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin；auditor只读</t>
+          <t>owner/admin/security_admin应用；auditor只读</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_security/platform_compliance/release_manager发布</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>现有dlp.read及log_only/block规则</t>
+          <t>GET /policy-templates；POST /policy-templates/{policy_template_id}/apply；内置模板、适配和绑定事实</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/117/146</t>
+          <t>PRD-117/119/143/146</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Provider前失败关闭；命中证据不保存Prompt/Response正文</t>
+          <t>企业不能篡改内置模板；套用产生tenant-scoped版本并可回滚</t>
         </is>
       </c>
     </row>
@@ -4149,27 +4149,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>intent-security</t>
+          <t>dlp-rules</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>敏感意图分类</t>
+          <t>DLP 规则</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>企业保留并降级</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>安全管理员测试工具</t>
+          <t>企业DLP</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>security_admin；owner/admin按权限</t>
+          <t>owner/admin/security_admin；auditor只读</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4179,17 +4179,17 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>现有intent_risk.classify；本地轻量规则</t>
+          <t>现有dlp.read及log_only/block规则</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>PRD-110/146</t>
+          <t>PRD-108/117/146</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>不作为普通导航；结果不含原文/命中片段；限流与审计</t>
+          <t>Provider前失败关闭；命中证据不保存Prompt/Response正文</t>
         </is>
       </c>
     </row>
@@ -4201,47 +4201,47 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>session-risks</t>
+          <t>intent-security</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>高危会话</t>
+          <t>敏感意图分类</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留并降级</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>企业会话风险处置</t>
+          <t>安全管理员测试工具</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin；auditor只读</t>
+          <t>security_admin；owner/admin按权限</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>platform_support仅经SupportGrant看固定摘要</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>现有session_risk.read及冻结/审批记录</t>
+          <t>现有intent_risk.classify；本地轻量规则</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>PRD-116/137/146</t>
+          <t>PRD-110/146</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>处置绑定Workspace并动态撤权；平台默认看不到会话正文</t>
+          <t>不作为普通导航；结果不含原文/命中片段；限流与审计</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>output-safety</t>
+          <t>session-risks</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>输出安全事件</t>
+          <t>高危会话</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>企业输出安全</t>
+          <t>企业会话风险处置</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>platform_security只看脱敏聚合</t>
+          <t>platform_support仅经SupportGrant看固定摘要</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>现有request_log.read的阻断/扫描事实</t>
+          <t>现有session_risk.read及冻结/审批记录</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/109/117/146</t>
+          <t>PRD-116/137/146</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>正文默认不持久化；事件含owner、code、request_id而非输出明文</t>
+          <t>处置绑定Workspace并动态撤权；平台默认看不到会话正文</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4305,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>webhooks</t>
+          <t>output-safety</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Webhook 设置</t>
+          <t>输出安全事件</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -4320,32 +4320,32 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>企业治理事件订阅</t>
+          <t>企业输出安全</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin</t>
+          <t>owner/admin/security_admin；auditor只读</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_security只看脱敏聚合</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>现有webhook.manage、Endpoint与签名Secret</t>
+          <t>现有request_log.read的阻断/扫描事实</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>PRD-105/133/146</t>
+          <t>PRD-108/109/117/146</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>签名Secret只显示一次；SSRF、重放、出站ACL和审计通过</t>
+          <t>正文默认不持久化；事件含owner、code、request_id而非输出明文</t>
         </is>
       </c>
     </row>
@@ -4357,22 +4357,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>webhook-dead-letters</t>
+          <t>webhooks</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Webhook 死信</t>
+          <t>Webhook 设置</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>企业保留并降级</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>企业高级运维入口</t>
+          <t>企业治理事件订阅</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -4387,17 +4387,17 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>现有webhook.manage、持久死信与安全重放</t>
+          <t>现有webhook.manage、Endpoint与签名Secret</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>PRD-106/146</t>
+          <t>PRD-105/133/146</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>不默认出现在普通导航；重放幂等、限次且不能修改冻结payload</t>
+          <t>签名Secret只显示一次；SSRF、重放、出站ACL和审计通过</t>
         </is>
       </c>
     </row>
@@ -4409,99 +4409,99 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>audit-logs</t>
+          <t>webhook-dead-letters</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>审计日志</t>
+          <t>Webhook 死信</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>企业保留；平台审计拆分</t>
+          <t>企业保留并降级</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>企业不可变审计</t>
+          <t>企业高级运维入口</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin/legal_admin/auditor</t>
+          <t>owner/admin/security_admin</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>各platform_*只见自身平台审计；支持受Grant限制</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>现有audit.read及不可变audit_logs</t>
+          <t>现有webhook.manage、持久死信与安全重放</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>PRD-095/117/135/145/146</t>
+          <t>PRD-106/146</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>平台和企业审计域分离；Key/Token/Prompt/Response不入证据</t>
+          <t>不默认出现在普通导航；重放幂等、限次且不能修改冻结payload</t>
         </is>
       </c>
     </row>
     <row r="46" ht="108" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>调用与成本</t>
+          <t>安全与治理</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>request-logs</t>
+          <t>audit-logs</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>调用日志</t>
+          <t>审计日志</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留；平台审计拆分</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>企业调用可观测性</t>
+          <t>企业不可变审计</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/security_admin/auditor/viewer按字段</t>
+          <t>owner/admin/security_admin/legal_admin/auditor</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>platform_support仅JIT白名单摘要</t>
+          <t>各platform_*只见自身平台审计；支持受Grant限制</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>现有request_log.read及分页/trace</t>
+          <t>现有audit.read及不可变audit_logs</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>PRD-109/117/146</t>
+          <t>PRD-095/117/135/145/146</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>只加载当前页；正文/Secret不记录；失败与用量成本可关联</t>
+          <t>平台和企业审计域分离；Key/Token/Prompt/Response不入证据</t>
         </is>
       </c>
     </row>
@@ -4513,27 +4513,27 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>request-explanations</t>
+          <t>request-logs</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>请求解释</t>
+          <t>调用日志</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>企业保留并入日志详情</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>调用日志详情的路由/策略/成本解释</t>
+          <t>企业调用可观测性</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/security_admin/finance_admin/auditor按字段</t>
+          <t>owner/admin/developer/security_admin/auditor/viewer按字段</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>现有request_explanation.read</t>
+          <t>现有request_log.read及分页/trace</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>PRD-108/109/146</t>
+          <t>PRD-109/117/146</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；解释字段按职能裁剪；不能通过解释恢复Prompt/Response或Key</t>
+          <t>只加载当前页；正文/Secret不记录；失败与用量成本可关联</t>
         </is>
       </c>
     </row>
@@ -4565,99 +4565,99 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>feedback-summary</t>
+          <t>request-explanations</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>反馈报表</t>
+          <t>请求解释</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留并入日志详情</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>企业模型反馈与质量</t>
+          <t>调用日志详情的路由/策略/成本解释</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/viewer按权限</t>
+          <t>owner/admin/developer/security_admin/finance_admin/auditor按字段</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>platform_customer_success只读脱敏采用摘要，不读反馈正文</t>
+          <t>platform_support仅JIT白名单摘要</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>现有feedback.use及聚合报表</t>
+          <t>现有request_explanation.read</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>PRD-109/140/146</t>
+          <t>PRD-108/109/146</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>企业反馈不成为平台个体画像；跨域只传最小聚合</t>
+          <t>不占普通一级导航；解释字段按职能裁剪；不能通过解释恢复Prompt/Response或Key</t>
         </is>
       </c>
     </row>
     <row r="49" ht="108" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>开发者</t>
+          <t>调用与成本</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>quickstart</t>
+          <t>feedback-summary</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>快速开始</t>
+          <t>反馈报表</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>企业保留并任务化</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>角色化初始化向导</t>
+          <t>企业模型反馈与质量</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer</t>
+          <t>owner/admin/developer/viewer按权限</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>platform_support只协助脱敏状态</t>
+          <t>platform_customer_success只读脱敏采用摘要，不读反馈正文</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>现有developer_portal.read；静态步骤改为真实后端完成事实</t>
+          <t>现有feedback.use及聚合报表</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>PRD-097/146</t>
+          <t>PRD-109/140/146</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>步骤可点击、可查看证据、失败可恢复，不以假数据标记已完成</t>
+          <t>企业反馈不成为平台个体画像；跨域只传最小聚合</t>
         </is>
       </c>
     </row>
@@ -4669,47 +4669,47 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>sdk-examples</t>
+          <t>quickstart</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>SDK 示例</t>
+          <t>快速开始</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>企业保留并入开发者中心</t>
+          <t>企业保留并任务化</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>开发者中心的SDK示例</t>
+          <t>角色化初始化向导</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>developer；owner/admin按需</t>
+          <t>owner/admin/developer</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_support只协助脱敏状态</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>现有developer_portal.read及示例</t>
+          <t>现有developer_portal.read；静态步骤改为真实后端完成事实</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>PRD-133/146</t>
+          <t>PRD-097/146</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；示例使用占位值，不含真实Key；与N/N-1合同一致</t>
+          <t>步骤可点击、可查看证据、失败可恢复，不以假数据标记已完成</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>migration-guide</t>
+          <t>sdk-examples</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>迁移指南</t>
+          <t>SDK 示例</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4736,32 +4736,32 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>开发者中心的迁移兼容指南</t>
+          <t>开发者中心的SDK示例</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer</t>
+          <t>developer；owner/admin按需</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>platform_support可见公开内容</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>现有developer_portal.read；迁移平台兼容说明</t>
+          <t>现有developer_portal.read及示例</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>PRD-131/133/146</t>
+          <t>PRD-133/146</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；OpenRouter/硅基流动仅作为迁移兼容对象，不列为默认上游</t>
+          <t>不占普通一级导航；示例使用占位值，不含真实Key；与N/N-1合同一致</t>
         </is>
       </c>
     </row>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>api-docs</t>
+          <t>migration-guide</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>API 文档</t>
+          <t>迁移指南</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -4788,136 +4788,136 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>开发者中心的API文档</t>
+          <t>开发者中心的迁移兼容指南</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>developer；owner/admin按需</t>
+          <t>owner/admin/developer</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>platform_support只见公开合同</t>
+          <t>platform_support可见公开内容</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>现有console.basic.read；API合同与SDK版本</t>
+          <t>现有developer_portal.read；迁移平台兼容说明</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>PRD-133/146</t>
+          <t>PRD-131/133/146</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；文档示例无Secret；错误码/request_id、版本和废弃期明确</t>
+          <t>不占普通一级导航；OpenRouter/硅基流动仅作为迁移兼容对象，不列为默认上游</t>
         </is>
       </c>
     </row>
     <row r="53" ht="108" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>帮助中心</t>
+          <t>开发者</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>competitor-comparison</t>
+          <t>api-docs</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>竞品对比</t>
+          <t>API 文档</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>迁出产品控制台</t>
+          <t>企业保留并入开发者中心</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>平台市场/销售内容或外部文档</t>
+          <t>开发者中心的API文档</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>developer；owner/admin按需</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>platform_growth/platform_channel只管理已审核内容</t>
+          <t>platform_support只见公开合同</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>当前主要为console-web静态render，无租户业务API</t>
+          <t>现有console.basic.read；API合同与SDK版本</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>PRD-141/146/147</t>
+          <t>PRD-133/146</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>企业登录后产品UI不展示销售对比；迁移兼容说明仍可在迁移指南出现</t>
+          <t>不占普通一级导航；文档示例无Secret；错误码/request_id、版本和废弃期明确</t>
         </is>
       </c>
     </row>
     <row r="54" ht="108" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>开发者</t>
+          <t>帮助中心</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>enterprise-chat</t>
+          <t>competitor-comparison</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>企业 Chat</t>
+          <t>竞品对比</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>迁出产品控制台</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>企业AI应用</t>
+          <t>平台市场/销售内容或外部文档</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>获授权业务用户；配置由owner/admin/developer</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_growth/platform_channel只管理已审核内容</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>现有chat.use及企业会话owner</t>
+          <t>当前主要为console-web静态render，无租户业务API</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>PRD-116/117/146</t>
+          <t>PRD-141/146/147</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>会话和正文按租户策略处理；不同职能页面与动作不同</t>
+          <t>企业登录后产品UI不展示销售对比；迁移兼容说明仍可在迁移指南出现</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>prompt-templates</t>
+          <t>enterprise-chat</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Prompt 模板</t>
+          <t>企业 Chat</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4944,32 +4944,32 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>企业Prompt资产</t>
+          <t>企业AI应用</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer及获授权用户</t>
+          <t>获授权业务用户；配置由owner/admin/developer</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>platform_support无正文</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>现有prompt_template.read及企业模板库</t>
+          <t>现有chat.use及企业会话owner</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>PRD-117/146</t>
+          <t>PRD-116/117/146</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Prompt不得进入日志或验收证据；版本/权限/审计绑定tenant</t>
+          <t>会话和正文按租户策略处理；不同职能页面与动作不同</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>prompt-templates</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>文件处理</t>
+          <t>Prompt 模板</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>企业文件调用工具</t>
+          <t>企业Prompt资产</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -5011,121 +5011,121 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>现有file.read、提取与处理任务</t>
+          <t>现有prompt_template.read及企业模板库</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>PRD-117/122/146</t>
+          <t>PRD-117/146</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>文件正文、对象路径和提取文本受驻留/保留/DLP约束</t>
+          <t>Prompt不得进入日志或验收证据；版本/权限/审计绑定tenant</t>
         </is>
       </c>
     </row>
     <row r="57" ht="108" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>安全与治理</t>
+          <t>开发者</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>file-security</t>
+          <t>files</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>文件安全报告</t>
+          <t>文件处理</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>企业保留并入详情</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>文件详情与安全中心</t>
+          <t>企业文件调用工具</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/security_admin/developer/auditor按字段</t>
+          <t>owner/admin/developer及获授权用户</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>platform_security只看脱敏聚合</t>
+          <t>platform_support无正文</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>现有file.read、0066 outbox恢复事实</t>
+          <t>现有file.read、提取与处理任务</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>PRD-117/122/137/146</t>
+          <t>PRD-117/122/146</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；不重复实现PRD-073；报告不含正文，outbox水位可恢复</t>
+          <t>文件正文、对象路径和提取文本受驻留/保留/DLP约束</t>
         </is>
       </c>
     </row>
     <row r="58" ht="108" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>开发者</t>
+          <t>安全与治理</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>batch-jobs</t>
+          <t>file-security</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>批处理任务</t>
+          <t>文件安全报告</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>企业保留</t>
+          <t>企业保留并入详情</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>企业异步批处理</t>
+          <t>文件详情与安全中心</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer；finance/auditor只读归属摘要</t>
+          <t>owner/admin/security_admin/developer/auditor按字段</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>platform_ops只看平台队列健康</t>
+          <t>platform_security只看脱敏聚合</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>现有batch.read、0067 Scheduler/Worker</t>
+          <t>现有file.read、0066 outbox恢复事实</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>PRD-106/113/146</t>
+          <t>PRD-117/122/137/146</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>job/lease/副作用均带tenant owner；企业看不到其他租户或平台队列内部</t>
+          <t>不占普通一级导航；不重复实现PRD-073；报告不含正文，outbox水位可恢复</t>
         </is>
       </c>
     </row>
@@ -5137,203 +5137,203 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>mcp-tools</t>
+          <t>batch-jobs</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>MCP 工具</t>
+          <t>批处理任务</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>企业保留并入开发者中心</t>
+          <t>企业保留</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>开发者中心的MCP治理</t>
+          <t>企业异步批处理</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/security_admin按权限</t>
+          <t>owner/admin/developer；finance/auditor只读归属摘要</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_ops只看平台队列健康</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>现有mcp.read及注册/权限/网络ACL</t>
+          <t>现有batch.read、0067 Scheduler/Worker</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>PRD-110/117/118/146</t>
+          <t>PRD-106/113/146</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>不占普通一级导航；工具scope、出站网络和机器身份最小授权；Secret不入日志</t>
+          <t>job/lease/副作用均带tenant owner；企业看不到其他租户或平台队列内部</t>
         </is>
       </c>
     </row>
     <row r="60" ht="108" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>租户治理</t>
+          <t>开发者</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>tenant-data-lifecycle</t>
+          <t>mcp-tools</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>数据管理</t>
+          <t>MCP 工具</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>企业保留并改名</t>
+          <t>企业保留并入开发者中心</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Workspace数据与隐私</t>
+          <t>开发者中心的MCP治理</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>owner/legal_admin/security_admin/auditor按动作</t>
+          <t>owner/admin/developer/security_admin按权限</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>platform_privacy只处理全局账号请求和最小队列</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>现有tenant_data.read、导出/删除/注销状态</t>
+          <t>现有mcp.read及注册/权限/网络ACL</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>PRD-117/134/146</t>
+          <t>PRD-110/117/118/146</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>复核tenant_data_states；导出/删除不允许平台支持绕过客户授权</t>
+          <t>不占普通一级导航；工具scope、出站网络和机器身份最小授权；Secret不入日志</t>
         </is>
       </c>
     </row>
     <row r="61" ht="108" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>开发者</t>
+          <t>租户治理</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>debug-console</t>
+          <t>tenant-data-lifecycle</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>OpenAI 调试台</t>
+          <t>数据管理</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>企业保留并降级</t>
+          <t>企业保留并改名</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>开发者高级工具</t>
+          <t>Workspace数据与隐私</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>developer；owner/admin按权限</t>
+          <t>owner/legal_admin/security_admin/auditor按动作</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>platform_privacy只处理全局账号请求和最小队列</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>现有debug_console.use；真实Gateway调用</t>
+          <t>现有tenant_data.read、导出/删除/注销状态</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>PRD-110/133/146</t>
+          <t>PRD-117/134/146</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>默认不向非开发角色展示；Key/Prompt/Response不进入日志或验收证据</t>
+          <t>复核tenant_data_states；导出/删除不允许平台支持绕过客户授权</t>
         </is>
       </c>
     </row>
     <row r="62" ht="108" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>系统</t>
+          <t>开发者</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>system-status</t>
+          <t>debug-console</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>系统状态</t>
+          <t>OpenAI 调试台</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>平台/企业拆分</t>
+          <t>企业保留并降级</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Workspace服务状态；平台SRE状态</t>
+          <t>开发者高级工具</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>owner/admin/developer/viewer按授权</t>
+          <t>developer；owner/admin按权限</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>platform_ops/platform_support/platform_owner</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>现有console.basic.read/provider status；平台另建Cell/Fleet/依赖状态</t>
+          <t>现有debug_console.use；真实Gateway调用</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>PRD-109/112/145</t>
+          <t>PRD-110/133/146</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>企业只见与自身相关的可操作状态；平台状态不暴露客户业务数据</t>
+          <t>默认不向非开发角色展示；Key/Prompt/Response不进入日志或验收证据</t>
         </is>
       </c>
     </row>
@@ -5345,47 +5345,47 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>language-settings</t>
+          <t>system-status</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>语言设置</t>
+          <t>系统状态</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>迁到全局账号壳层</t>
+          <t>平台/企业拆分</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>GlobalAccount偏好</t>
+          <t>Workspace服务状态；平台SRE状态</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>所有交互式账号本人</t>
+          <t>owner/admin/developer/viewer按授权</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>所有平台交互式账号本人</t>
+          <t>platform_ops/platform_support/platform_owner</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>现有user_preferences；不再作为tenant业务页面</t>
+          <t>现有console.basic.read/provider status；平台另建Cell/Fleet/依赖状态</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>PRD-091/105/145</t>
+          <t>PRD-109/112/145</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>语言不携带tenant角色、不改变权限；跨Workspace一致且可回退</t>
+          <t>企业只见与自身相关的可操作状态；平台状态不暴露客户业务数据</t>
         </is>
       </c>
     </row>
@@ -5397,52 +5397,104 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
+          <t>language-settings</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>语言设置</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>迁到全局账号壳层</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>GlobalAccount偏好</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>所有交互式账号本人</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>所有平台交互式账号本人</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>现有user_preferences；不再作为tenant业务页面</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>PRD-091/105/145</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>语言不携带tenant角色、不改变权限；跨Workspace一致且可回退</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="108" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
           <t>config-summary</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>环境信息</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>平台/企业拆分并降级</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Deployment诊断；平台运行配置摘要</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>owner/admin/developer高级入口；auditor只读脱敏</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>platform_ops/platform_security；support需Grant</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>GET /internal/config/summary；当前system.config.read</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>PRD-109/120/125/145/147</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>普通用户不见环境变量、路径、内部token或研发配置；平台和企业DTO白名单分离</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J64"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9633,7 +9685,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -13133,7 +13185,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>以现有63项导航处置矩阵重组企业Gateway：默认折叠并保持单组展开；首页按角色显示下一步任务；保留BYOK、Provider/模型/路由/评测、Project/Application、Virtual Key、额度预算、用量成本、企业内部财务、员工权限、安全策略、日志审计、Prompt、文件与文件安全、企业异步批处理、MCP、数据生命周期和私有部署；competitor-comparison移出产品UI；debug、intent测试、Webhook死信、环境诊断等仅高级角色按需进入。</t>
+          <t>以现有64项导航处置矩阵重组企业Gateway：默认折叠并保持单组展开；首页按角色显示下一步任务；保留BYOK、Provider/模型/路由/评测、Project/Application、Virtual Key、额度预算、用量成本、企业内部财务、员工权限、安全策略、日志审计、Prompt、文件与文件安全、企业异步批处理、MCP、数据生命周期和私有部署；competitor-comparison移出产品UI；debug、intent测试、Webhook死信、环境诊断等仅高级角色按需进入。</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -13173,7 +13225,7 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>63项现状导航每项有唯一处置且源码清单无遗漏；所有企业角色只看职责相关页；默认折叠、单组展开、直达URL负测试、真人鼠标主流程、390/1280/1440布局和无研发术语通过；每页只加载当前数据。</t>
+          <t>64项现状导航每项有唯一处置且源码清单无遗漏；所有企业角色只看职责相关页；默认折叠、单组展开、直达URL负测试、真人鼠标主流程、390/1280/1440布局和无研发术语通过；每页只加载当前数据。</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
@@ -13265,7 +13317,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>按63项导航处置矩阵对代码、API、权限、表、事件、Scheduler、导航、DOM、文案、遥测和审计执行expand/dual-read/backfill/cutover/contract。盘点control_background_schedulers_enabled当前统一开关下安装的23个后台循环，逐个迁移执行身份、queue owner、lease和水位；Web副本不重复承担无界Worker。平台接管运营、品牌、Provider工程和商业目录；企业保留AI治理；拆分页使用独立主体；退役页面设置固定tombstone，不直接删除历史tenant_id事实。</t>
+          <t>按64项导航处置矩阵对代码、API、权限、表、事件、Scheduler、导航、DOM、文案、遥测和审计执行expand/dual-read/backfill/cutover/contract。盘点control_background_schedulers_enabled当前统一开关下安装的23个后台循环，逐个迁移执行身份、queue owner、lease和水位；Web副本不重复承担无界Worker。平台接管运营、品牌、Provider工程和商业目录；企业保留AI治理；拆分页使用独立主体；退役页面设置固定tombstone，不直接删除历史tenant_id事实。</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -13439,7 +13491,7 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>PRD-090..147全部完成；63项导航处置落地；平台/企业/伙伴/支持/设备五域负测试通过；WB/API/BB/GR/PERF/WEB/UI/UCD/COMP/SEC/FLOW全组通过；72小时无P0/P1；README/Excel/docs/HEAD/origin一致。</t>
+          <t>PRD-090..147全部完成；64项导航处置落地；平台/企业/伙伴/支持/设备五域负测试通过；WB/API/BB/GR/PERF/WEB/UI/UCD/COMP/SEC/FLOW全组通过；72小时无P0/P1；README/Excel/docs/HEAD/origin一致。</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
@@ -13826,7 +13878,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>G7通过；63项导航唯一处置、历史保真、企业旧平台入口归零</t>
+          <t>G7通过；64项导航唯一处置、历史保真、企业旧平台入口归零</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -45093,7 +45145,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>源码63项导航处置100%；平台运营/品牌/Provider工程/商业账务分域；历史行数/hash/outbox/Scheduler/审计水位保真；企业旧平台入口、DOM、预取/API归零</t>
+          <t>源码64项导航处置100%；平台运营/品牌/Provider工程/商业账务分域；历史行数/hash/outbox/Scheduler/审计水位保真；企业旧平台入口、DOM、预取/API归零</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..120已完成，下一项PRD-121。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..121已完成，下一项PRD-122。</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..121已完成，下一项PRD-122。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..122已完成，下一项PRD-123。</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..122已完成，下一项PRD-123。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..123已完成，下一项PRD-124。</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..123已完成，下一项PRD-124。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..124已完成，下一项PRD-125。</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..126已完成，下一项PRD-127。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..127已完成，下一项PRD-128。</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..127已完成，下一项PRD-128。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..128已完成，下一项PRD-129。</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..128已完成，下一项PRD-129。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..129已完成，下一项PRD-130。</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..129已完成，下一项PRD-130。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..130已完成，下一项PRD-131。</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..130已完成，下一项PRD-131。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..131已完成，下一项PRD-132。</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..131已完成，下一项PRD-132。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..132已完成，下一项PRD-133。</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..132已完成，下一项PRD-133。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..133已完成，下一项PRD-134。</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..133已完成，下一项PRD-134。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..134已完成，下一项PRD-135。</t>
         </is>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..134已完成，下一项PRD-135。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..135已完成，下一项PRD-136。</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..135已完成，下一项PRD-136。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..136已完成，下一项PRD-137。</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..136已完成，下一项PRD-137。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..137已完成，下一项PRD-138。</t>
         </is>
       </c>
     </row>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..137已完成，下一项PRD-138。</t>
+          <t>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..138已完成，下一项PRD-139。</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R64bb2c79b3724e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Rfee5d2c0905a4eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rf8303728f1cf4f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Rdd60e6766d8c4d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Re8493e0572ff4d3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R818012bc057e4d6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Ra7838a5356424bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R8b6c2c9acbe64ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R55affd35cffe4b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R51ffb1d324394f0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Re80e50c34b3d4c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R324f2b1ad4ab4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rac5dd899cc904de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R01202a715a5d4450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Re1608f03f7954cf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R11e4c47c67e640a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rcce441d4135f48e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Re5a72eba047845c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rbb1718ba1ea94ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R7465468275ee46fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3664c4baa4be4a6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="Re72ec8c2e7404f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Ra59e612c5af24651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R2dcde77f2fef4b82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..139已完成，下一项PRD-140。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..140已完成，下一项PRD-141。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12208,10 +12208,8 @@
           <x:t xml:space="preserve">PRD-140</x:t>
         </x:is>
       </x:c>
-      <x:c r="B52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B52" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C52" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rac5dd899cc904de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R01202a715a5d4450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Re1608f03f7954cf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R11e4c47c67e640a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rcce441d4135f48e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Re5a72eba047845c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rbb1718ba1ea94ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R7465468275ee46fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3664c4baa4be4a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="Re72ec8c2e7404f9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Ra59e612c5af24651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R2dcde77f2fef4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R06be0fb7952d40f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R39cbe3a0f11c4a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R78f68893b6864837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Rb98cfbb98bf24b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R87201ba0249344e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rff777d4fa6844d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rcfb1392baea64895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rcf35237fcaf34d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R357755051f404572"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R65ab2760129f40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R723397d426f545e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Rc4184d1ad8f04963"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..140已完成，下一项PRD-141。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..141已完成，下一项PRD-142。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12340,10 +12340,8 @@
           <x:t xml:space="preserve">PRD-141</x:t>
         </x:is>
       </x:c>
-      <x:c r="B53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B53" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C53" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R06be0fb7952d40f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R39cbe3a0f11c4a06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R78f68893b6864837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Rb98cfbb98bf24b48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R87201ba0249344e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rff777d4fa6844d16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rcfb1392baea64895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rcf35237fcaf34d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R357755051f404572"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R65ab2760129f40da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R723397d426f545e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Rc4184d1ad8f04963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R77cac4b140fa472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R0dc41c84753c4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R4855061cfde74634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R81227b6ccf2045ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rb10c5a06a84c46d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R6eabba15f009452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rff29055813d44925"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rc3a42042d86d4a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R57293fa79cfb4e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R96eb75f0b08b4f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rfd4563f088fd4215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R34e6ad1ddd234178"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..141已完成，下一项PRD-142。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..142已完成，下一项PRD-143。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12472,10 +12472,8 @@
           <x:t xml:space="preserve">PRD-142</x:t>
         </x:is>
       </x:c>
-      <x:c r="B54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B54" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R77cac4b140fa472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R0dc41c84753c4145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R4855061cfde74634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R81227b6ccf2045ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rb10c5a06a84c46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R6eabba15f009452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rff29055813d44925"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rc3a42042d86d4a49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R57293fa79cfb4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R96eb75f0b08b4f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rfd4563f088fd4215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R34e6ad1ddd234178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Ra759a73c26bf479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R3b4d3c9bdf044dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rfa5f07e1d1b14ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R8679731bad8140a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Re9961c636cd249f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9041d03756484a5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R8a486bdba54b4556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R11354e4710434ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R18d053ffbc8f4eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R74b13362eb4347c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R3b039e6ff3dd4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R94de466ebb9d4b96"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..142已完成，下一项PRD-143。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..143已完成，下一项PRD-144。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12603,10 +12603,8 @@
           <x:t xml:space="preserve">PRD-143</x:t>
         </x:is>
       </x:c>
-      <x:c r="B55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B55" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Ra759a73c26bf479e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R3b4d3c9bdf044dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rfa5f07e1d1b14ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R8679731bad8140a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Re9961c636cd249f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9041d03756484a5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R8a486bdba54b4556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R11354e4710434ed0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R18d053ffbc8f4eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R74b13362eb4347c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R3b039e6ff3dd4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R94de466ebb9d4b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R47703a60e27f4714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R8b1ae693ec8b4d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R96eca7b8039e4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R7c7778e4bed0438b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R5f0cf32c623d4777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rd69dc284851344b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rc5cb9153156845f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R21d3e38967cc4fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R4140185e03e34985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="Rcabd12c2b38a43b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rd29432c7cecf45a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Rc67f4f18eb6c4ed6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..143已完成，下一项PRD-144。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..144已完成，下一项PRD-145。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12734,10 +12734,8 @@
           <x:t xml:space="preserve">PRD-144</x:t>
         </x:is>
       </x:c>
-      <x:c r="B56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B56" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R47703a60e27f4714"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R8b1ae693ec8b4d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R96eca7b8039e4770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R7c7778e4bed0438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R5f0cf32c623d4777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rd69dc284851344b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rc5cb9153156845f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R21d3e38967cc4fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R4140185e03e34985"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="Rcabd12c2b38a43b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rd29432c7cecf45a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Rc67f4f18eb6c4ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R82ef92b78db94a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R2b6180e4dfda403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R23dcdc08fc444285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra3ec45c5026a421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R78d96374833f4b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R00e7278bfdff42bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R4db231eadbb047ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R9bed2f393daf4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R0c3a0260669f438c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R97d8ec3fb6394e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R4dc547e900df476f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R69d4e560aa954f75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12868,10 +12868,8 @@
           <x:t xml:space="preserve">PRD-145</x:t>
         </x:is>
       </x:c>
-      <x:c r="B57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B57" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C57" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R82ef92b78db94a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R2b6180e4dfda403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R23dcdc08fc444285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra3ec45c5026a421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R78d96374833f4b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R00e7278bfdff42bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R4db231eadbb047ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R9bed2f393daf4c15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R0c3a0260669f438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R97d8ec3fb6394e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R4dc547e900df476f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R69d4e560aa954f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rc35b1edb065c495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R1b28908f205d4558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R6056d875b226423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R22d3833ddeee420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rd47234083ec14e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rdd8b56a3fc414c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R18fc9c3de201407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R0321793042cf43c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R6ad945780a464fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R3ef7f5f3feba4f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R8b1731da60624f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R4ec0a838e4f64628"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13003,10 +13003,8 @@
           <x:t xml:space="preserve">PRD-146</x:t>
         </x:is>
       </x:c>
-      <x:c r="B58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B58" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rc35b1edb065c495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R1b28908f205d4558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R6056d875b226423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R22d3833ddeee420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rd47234083ec14e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rdd8b56a3fc414c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R18fc9c3de201407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R0321793042cf43c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R6ad945780a464fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R3ef7f5f3feba4f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R8b1731da60624f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R4ec0a838e4f64628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rfa2c5606aef148da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Rb016899674114404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R4fec6e75b3d4444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra7243af2d87e4de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R248bfbb46ff84783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9451ac55382544f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R317c9174a3514a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R319707f56f554e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3286ed95b7ed4742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R16576c5d82744846"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R270cc2e3966b4f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R8e52e184329d450d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..144已完成，下一项PRD-145。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..147已完成；G7未通过，PRD-148不得开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -13133,10 +13133,8 @@
           <x:t xml:space="preserve">PRD-147</x:t>
         </x:is>
       </x:c>
-      <x:c r="B59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B59" s="3" t="str">
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="C59" s="3" t="inlineStr">
         <x:is>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rfa2c5606aef148da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Rb016899674114404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R4fec6e75b3d4444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra7243af2d87e4de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="R248bfbb46ff84783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9451ac55382544f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R317c9174a3514a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R319707f56f554e4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3286ed95b7ed4742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R16576c5d82744846"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R270cc2e3966b4f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R8e52e184329d450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rb963afd9481e4104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Rfbb2fd4117fa4d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Ra7d6d92f3bc14b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra8dbe04b3d814bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rd01dccbdfa614196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R34a9669ad53943cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rfeb2c6bc90424e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rba988ef8e8e64e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R2a5b4bec899f4424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R79e85458fb8b46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rc3c28563ed104cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R0155f0b4fab84bb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；兼容旧状态all_108_prds_complete=false；PRD-090..147已完成；G7未通过，PRD-148不得开始。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；all_108_prds_complete=false；PRD-090..147实现完成，G7通过；G6缺72小时观测，PRD-148未启动。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rb963afd9481e4104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Rfbb2fd4117fa4d90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Ra7d6d92f3bc14b8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="Ra8dbe04b3d814bcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rd01dccbdfa614196"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R34a9669ad53943cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rfeb2c6bc90424e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rba988ef8e8e64e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R2a5b4bec899f4424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R79e85458fb8b46b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rc3c28563ed104cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R0155f0b4fab84bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R8e9069ceebf04dae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R28e71eecd84d44a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rffe52f200c114190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R52e4f618e6874abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rbe2171a25ab44d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9d9d034524ac40ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rcdda437450b84110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R87ba0941e9b14b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R508b5ca5d0f24425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R355b67ce237e4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rd0631111cf844010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R9dcc7e6799e74cee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；all_108_prds_complete=false；PRD-090..147实现完成，G7通过；G6缺72小时观测，PRD-148未启动。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；all_108_prds_complete=false；PRD-090..147已有交付，G7通过；G6补实现、原生业务及72小时真实证据，PRD-148未启动。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R8e9069ceebf04dae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R28e71eecd84d44a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rffe52f200c114190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R52e4f618e6874abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rbe2171a25ab44d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="R9d9d034524ac40ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Rcdda437450b84110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R87ba0941e9b14b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R508b5ca5d0f24425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R355b67ce237e4923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="Rd0631111cf844010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="R9dcc7e6799e74cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rec17cac352c04a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R1d807fc06b734ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rcf6212f6fc2d43ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R1ae7beff4ae9492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Ra278a458c0db4ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rf93a810891eb4b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R5b47cef0194c42a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rcc86d3f6d5a946a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3e2f8e58bda349be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R9866fafe8f254c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R51046280cffa4a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Ra4e58e5982464dbb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,14 +467,18 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" ht="38" customHeight="1">
+    <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">总体状态</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>saas_incremental_roadmap_complete=false；all_108_prds_complete=false；PRD-090..147已有交付，G7通过；G6补实现、原生业务及72小时真实证据，PRD-148未启动。</x:v>
+        <x:v>saas_incremental_roadmap_complete=false；all_108_prds_complete=false；2026-09-19 PRD-148：源码 bdb3204a...bb838（2689 文件）；page-visit 7/7。真实浏览器组织链未形成通过，保留 Chromium 登出 15 秒失败、page-visit 待完成和浏览器上下文异常；验收夹具查询参数错配已修正。五域、付费/治理、会签/回滚、对账、259200 秒稳定性和 HEAD/origin 未闭合，PRD-148 保持未启动。证据：outputs/prd148-current-evidence-index-final-20260916.json。；2026-09-20 current acceptance checkpoint: 当前源码 SHA256 6713a21a301d9b7cfb526df7dcf5b53e98dfd79a82d869ef08a14c86d17c0392（2691 files）；分批角色走查 admin/developer/viewer 180/180 页通过，证据 .artifacts/product-qa/20260920-{admin,developer,viewer}-g{1,2,3}；Workspace page-visit 集成 7/7 通过，证据 outputs/prd148-page-visits-current-20260920-r2.xml。真实 S1 当前重放 outputs/prd148-real-s1-rerun-20260920.json / .artifacts/s1-browser-_dluz246 仍失败于 1280.onboarding-navigation.tenant：截图等待字体超时，6 个 page-view 请求未结束；注册、创建组织、Provider、邀请员工、个人 KEY、轮换、撤权及撤权后 401 已完成，但完整商业链路不能宣称通过。五域矩阵已有 113/113 通过且起止源码漂移，不能绑定当前源码；真实商业、六方会签、发布后复核、回滚、财务/隐私/安全/迁移对账、scheduler-enabled 259200 秒观察及 HEAD/origin 一致仍未闭合。PRD-148 保持未完成，01_PRD总表!B60 保持未启动。
+2026-09-20 当前源码多角色批量走查：admin/developer/viewer Workspace 180/180 页，FLOW-01/02/03，Platform 运营迁移/MFA，公共入口四视口通过；Partner 浏览器验收在页面操作前因旧 0080 迁移基线夹具与当前 0155 迁移头漂移失败，未计 Partner 通过。前端 Partner/Support 21/21、后端 10/10 聚焦回归通过。证据 outputs/prd148-human-role-batch-current-20260920-r3.json；PRD-148 仍未启动。
+2026-09-20 Partner 当前页面边界复验：隔离 Chromium 390x844 在无 ChannelMembership 账号下连续两次返回 403 partner.membership_required，页面访问撤销态、布局和错误边界通过；函数序列化属于夹具问题；正常 Workspace 进入 Partner 的混合 Cookie 冲突已复现为真实入口失败，尚未修复。旧 PRD-087 浏览器验收仍受 0080→0155 迁移基线漂移阻断。证据 .artifacts/product-qa/20260920-partner-r7/prd148-partner-audit-chromium-scale-1.json；PRD-148 仍未启动。
+2026-09-20 有数据复核：Support 空页面已修复，管理员/开发者表单创建、回复、升级、解决、评价、重开和持久化通过，查看者写入 403。Device 空页面、Partner 入口 400 仍失败。旧 human-r4 聚合漏算断言，撤回完整交互通过结论。Support/Device 后端 24/24，Support 前端 8/8。详见 docs/testing/PRD-148-populated-domain-audit-20260920.md；完整 QA、真实商业及会签/对账/72小时/HEAD-origin 门禁未闭合，PRD-148 未启动。
+2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -12075,8 +12079,10 @@
           <x:t xml:space="preserve">PRD-139</x:t>
         </x:is>
       </x:c>
-      <x:c r="B51" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B51" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C51" s="3" t="inlineStr">
         <x:is>
@@ -12208,8 +12214,10 @@
           <x:t xml:space="preserve">PRD-140</x:t>
         </x:is>
       </x:c>
-      <x:c r="B52" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B52" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C52" s="3" t="inlineStr">
         <x:is>
@@ -12340,8 +12348,10 @@
           <x:t xml:space="preserve">PRD-141</x:t>
         </x:is>
       </x:c>
-      <x:c r="B53" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B53" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C53" s="3" t="inlineStr">
         <x:is>
@@ -12472,8 +12482,10 @@
           <x:t xml:space="preserve">PRD-142</x:t>
         </x:is>
       </x:c>
-      <x:c r="B54" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B54" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C54" s="3" t="inlineStr">
         <x:is>
@@ -12603,8 +12615,10 @@
           <x:t xml:space="preserve">PRD-143</x:t>
         </x:is>
       </x:c>
-      <x:c r="B55" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B55" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C55" s="3" t="inlineStr">
         <x:is>
@@ -12734,8 +12748,10 @@
           <x:t xml:space="preserve">PRD-144</x:t>
         </x:is>
       </x:c>
-      <x:c r="B56" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B56" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C56" s="3" t="inlineStr">
         <x:is>
@@ -12868,8 +12884,10 @@
           <x:t xml:space="preserve">PRD-145</x:t>
         </x:is>
       </x:c>
-      <x:c r="B57" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B57" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C57" s="3" t="inlineStr">
         <x:is>
@@ -13003,8 +13021,10 @@
           <x:t xml:space="preserve">PRD-146</x:t>
         </x:is>
       </x:c>
-      <x:c r="B58" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B58" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C58" s="3" t="inlineStr">
         <x:is>
@@ -13133,8 +13153,10 @@
           <x:t xml:space="preserve">PRD-147</x:t>
         </x:is>
       </x:c>
-      <x:c r="B59" s="3" t="str">
-        <x:v>已完成</x:v>
+      <x:c r="B59" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="C59" s="3" t="inlineStr">
         <x:is>
@@ -13385,10 +13407,26 @@
           <x:t xml:space="preserve">后端2、前端1、测试1；按领域增加SRE/安全/财务/Agent 0.5-1</x:t>
         </x:is>
       </x:c>
-      <x:c r="Y60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设计文档、两轮编码前自审、迁移往返、专项测试、必要回归、真实 API/浏览器/运行验收、安全与禁止文件审计</x:t>
-        </x:is>
+      <x:c r="Y60" s="3" t="str">
+        <x:v>2026-09-15 当前源码复核：Platform 38/38、Workspace 62/62、Partner/Support 16 通过+1 退役路由 skipped、Device 14/14；GA/Gateway 40/40；源码 SHA256 4a8f9efb…700b08c2。外部付费/企业治理/私有 Gateway、六方会签/回滚/对账、正式 scheduler-enabled 72 小时仍缺证据。PRD-148 未完成。索引 outputs/prd148-current-evidence-index-after-cache-20260915.json。
+2026-09-15 迁移实况复核：PRD-148 未完成。本机入口 expanded/generation 0，分域迁移、对账、审批和退役记录均为空。64 条队列契约不能证明导航迁移完成。新源码 QA 仍运行中，10 处旧迁移基线和 PRD-147 历史子集修复仅已准备候选、未应用。真实商业、会签、发布回滚、对账、72 小时和 HEAD/origin 仍缺证据。详见 docs/testing/PRD-148-current.md 及 outputs/prd148-console-migration-audit-20260915.json。以下为历史记录。
+2026-09-15：PRD-148 未完成。修复 0155 回滚入口拒绝问题，GA 回归 14/14；副本往返保留 1094 表、543694 行。修复前 QA 15/15 任务、审计 95/97，PERF-08/10 缺长稳。新源码 9904e348…cebfe 的完整 QA 与五域回归运行中。真实商业/会签/发布回滚/对账、72 小时及 HEAD/origin 仍未闭合。见 docs/testing/PRD-148-current.md。以下为历史记录。
+2026-09-15 复核更正：PRD-148 未完成。五域选定用例及 Gateway 回归通过；4/4 仅 QA 合同，完整 QA 补跑中。formal10 已停止、GA 计入 0 秒；健康接口不能证明业务 72 小时及 0 P0/P1。当前结论见 docs/testing/PRD-148-current.md；下方保留历史记录。
+2026-09-15 正式观察已按 scheduler-enabled 配置启动：formal10 当前运行中，必须达到 259200 秒且 0 P0/P1，运行中不计为通过。详见 outputs/continuous-stability-20260915-formal10/status.json。
+2026-09-15 正式观察已按 scheduler-enabled 配置启动：formal9 当前运行 56.72 秒、354 请求、0 错误；必须达到 259200 秒且 0 P0/P1，运行中不计为通过。详见 outputs/continuous-stability-20260915-formal9/status.json。
+2026-09-15 当前：五域负向矩阵 112 passed + 1 retired skipped；Gateway 协议 27/27；11 组 QA 合同 4/4 任务通过，源码 SHA256 da72cabf…571e7a。真实浏览器矩阵/兼容性终验、真实付费/会签/回滚/对账、正式 72 小时、HEAD/origin 仍缺证据。PRD-148 未完成。索引 outputs/prd148-current-evidence-index-20260915.json。
+设计文档、两轮编码前自审、迁移往返、专项测试、必要回归、真实 API/浏览器/运行验收、安全与禁止文件审计
+2026-09-14：未完成，当前证据见 docs/testing/PRD-148-current.md
+2026-09-14 当前证据追加：Platform 矩阵 38/38，健康/就绪 6/6；调度器开启 5 分钟诊断 0 错误（非 72 小时证据）；PRD-148 仍未完成。详见 outputs/prd148-negative-platform-current2-20260914.xml、outputs/continuous-stability-20260914-diagnostic3/status.json、docs/testing/PRD-148-current.md。
+2026-09-14 当前证据追加：Platform 矩阵 38/38，Platform 并发单项 1/1，健康/就绪 6/6；formal3 已失败（120 秒、7 个错误），formal4-isolated 已按调度器开启配置启动但仍未完成 72 小时；PRD-148 仍未完成。详见 outputs/prd148-negative-current2-20260914/status.json、outputs/prd148-platform-concurrency-followup-20260914.xml、outputs/continuous-stability-20260914-formal3/status.json、outputs/continuous-stability-20260914-formal4-isolated/status.json、docs/testing/PRD-148-current.md。
+2026-09-14 当前证据追加：Platform 矩阵 38/38，Platform 并发单项 1/1，健康/就绪 6/6；formal3 已失败（120 秒、7 个错误），formal4-isolated 亦已失败（372 秒、7 个 Control 超时），隔离数据库仍复现调度器争用；PRD-148 仍未完成。详见 outputs/prd148-negative-current2-20260914/status.json、outputs/prd148-platform-concurrency-followup-20260914.xml、outputs/continuous-stability-20260914-formal3/status.json、outputs/continuous-stability-20260914-formal4-isolated/status.json、docs/testing/PRD-148-current.md。
+2026-09-14 当前证据追加：共享 SQLite 连接按库一次启用 WAL；scheduler-enabled 诊断 120 秒 704 请求 0 错误，仍不构成 GA。正式 formal6 已按源码 SHA256 8471d7a5e254a2b8775b6a302faeaadb5216b6ad1be3dee99c18cf7fb182580e 启动，当前运行中，必须达到 259200 秒且 0 P0/P1。PRD-095 session P95 61.6ms（门槛 &lt;50ms）保留为真实失败；套餐/订阅/权益、付费计量、六方会签、发布回滚和最终对账仍缺证据。详见 docs/testing/PRD-148-current.md。
+2026-09-15 当前证据追加：修复 PRD-145 审批游标非规范 Base64url 接受问题，Workspace 44/44 与 GA 生命周期 13/13 通过；此前 Platform/Partner/Support/Device 证据早于该修复，需重新绑定当前源码。formal6 750.7 秒、3 次 Control read_timeout 失败；付费计划/订阅/权益/用量账本、真实六方会签/发布回滚/对账和 259200 秒正式观察仍缺，PRD-148 保持未完成。索引 outputs/prd148-current-evidence-index-20260915.json。
+2026-09-15 进一步修复：PRD-140 customer-success 游标同样拒绝非规范 Base64url；Platform 当前 38/38 通过。Partner/Support 与 Device 尚需最终源码快照重绑定；商业付费、会签/回滚/对账和 259200 秒正式观察仍未完成。
+2026-09-15 当前源码 QA 追加：All 5/5（WB/API/BB/GR/SEC、隔离 PERF、WEB/UI/UCD/COMP/FLOW、lint、Chromium admin/developer/viewer），PERF smoke/pressure 3/3；GA 14/14、协议/默认路由 24/24。formal11 运行约3531秒/0 errors，要求259200秒，不计为GA；付费订阅/权益、企业治理/私有Gateway、六方会签/回滚/对账和HEAD/origin仍缺证据。索引 outputs/prd148-current-evidence-index-final-20260915.json。
+2026-09-18 当前源码页面域审计 69/69；PAGE-116 Workspace Cookie 本地模型页修复；证据 outputs/prd148-domain-ui-audit-current-20260918-r4/report.json。PRD-148 未完成，见 outputs/prd148-current-evidence-index-final-20260916.json。
+2026-09-18 资源摘要同步后的当前源码页面域审计 69/69；PAGE-116 Workspace Cookie 本地模型页修复；源码 0143b226e96aac094667d32d03e2fe3aef590369c1cdb99aafc262f1e65d9384，生产摘要 aa58650f6c0b3c7badaaa4c69f5f05cd8717f54bec32ab3187c10894518f318b，证据 outputs/prd148-domain-ui-audit-current-20260918-r5/report.json。PRD-148 未完成，见 outputs/prd148-current-evidence-index-final-20260916.json。
+2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
+++ b/企业级AI_Gateway_SaaS增量开发计划_PRD090起.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="Rec17cac352c04a1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="R1d807fc06b734ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="Rcf6212f6fc2d43ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R1ae7beff4ae9492a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Ra278a458c0db4ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rf93a810891eb4b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="R5b47cef0194c42a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="Rcc86d3f6d5a946a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R3e2f8e58bda349be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="R9866fafe8f254c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R51046280cffa4a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Ra4e58e5982464dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_变更说明" sheetId="1" r:id="R5ead969022ae44c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_PRD总表" sheetId="2" r:id="Re9505fcc022b45dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_阶段路线图" sheetId="3" r:id="R19e52cc520164adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_核心数据对象" sheetId="4" r:id="R2b068c91011241bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_API与事件" sheetId="5" r:id="Rea5b3b167b8d4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_角色权限矩阵" sheetId="6" r:id="Rca7d0034b0dc4ceb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_测试与验收计划" sheetId="7" r:id="Re909eeb0545c4692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_旧计划废弃映射" sheetId="8" r:id="R5952a5bef94c49c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_里程碑门禁" sheetId="9" r:id="R61f271fd1b114988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_风险与决策" sheetId="10" r:id="Rc1f7b562217e4ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_角色页面矩阵" sheetId="11" r:id="R0b39d09442fe4a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_现有导航处置" sheetId="12" r:id="Rf09a374ce0a44519"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -478,7 +478,8 @@
 2026-09-20 当前源码多角色批量走查：admin/developer/viewer Workspace 180/180 页，FLOW-01/02/03，Platform 运营迁移/MFA，公共入口四视口通过；Partner 浏览器验收在页面操作前因旧 0080 迁移基线夹具与当前 0155 迁移头漂移失败，未计 Partner 通过。前端 Partner/Support 21/21、后端 10/10 聚焦回归通过。证据 outputs/prd148-human-role-batch-current-20260920-r3.json；PRD-148 仍未启动。
 2026-09-20 Partner 当前页面边界复验：隔离 Chromium 390x844 在无 ChannelMembership 账号下连续两次返回 403 partner.membership_required，页面访问撤销态、布局和错误边界通过；函数序列化属于夹具问题；正常 Workspace 进入 Partner 的混合 Cookie 冲突已复现为真实入口失败，尚未修复。旧 PRD-087 浏览器验收仍受 0080→0155 迁移基线漂移阻断。证据 .artifacts/product-qa/20260920-partner-r7/prd148-partner-audit-chromium-scale-1.json；PRD-148 仍未启动。
 2026-09-20 有数据复核：Support 空页面已修复，管理员/开发者表单创建、回复、升级、解决、评价、重开和持久化通过，查看者写入 403。Device 空页面、Partner 入口 400 仍失败。旧 human-r4 聚合漏算断言，撤回完整交互通过结论。Support/Device 后端 24/24，Support 前端 8/8。详见 docs/testing/PRD-148-populated-domain-audit-20260920.md；完整 QA、真实商业及会签/对账/72小时/HEAD-origin 门禁未闭合，PRD-148 未启动。
-2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。</x:v>
+2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。
+2026-09-26 r45 用户使用容易度复验：中文管理员/开发者/查看者的概览、成员、模型服务、组织/个人 KEY 关键路径完成当前源码绑定的定向角色审计 15/15 与可逆鼠标键盘交互 15/15；0 页面、请求、响应、控制台、授权、标签、溢出、裁切、重叠或动作失败。管理员概览默认折叠空区域，成员为可搜索表格，Provider 自定义中转站入口默认收起，员工仅管理个人 KEY。单测 2259/2259，lint 842 files，build 295 assets，生产资源摘要 3a73b84e5fa3b021cc5b55ca3959ebda80ae17a00214a0f3f33be7001069dd53。证据 .artifacts/product-qa/20260926-usability-current-r45/ 与 .artifacts/product-qa/20260926-usability-human-r45/，源码 outputs/prd148-source-current-20260926-usability-r45.json。PRD-148 仍未完成，真实业务链路、GA 门禁、HEAD/origin 及其他缺失证据保持未闭合。\n2026-09-29 文案二次收口：员工接入页删除重复协议路径与个人 KEY 管理说明，自定义模型服务入口删除重复用途说明；文案审计 16 个候选（2 必要、14 复核），定向单测 88/88、lint 842 files、build 295 assets。源码 c2f8fb1dbf2ea88c53b995eb958b28e2f044aeb1b51bbc14a2fb090dd30eb9cb，资源摘要 eacf5b43d363109984db023a328731900e5f10586ef4c296ec0a5de0403b77c7。PRD-148 仍未完成；证据 outputs/prd148-current-evidence-index-final-20260929-r11.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -13286,10 +13287,8 @@
           <x:t xml:space="preserve">PRD-148</x:t>
         </x:is>
       </x:c>
-      <x:c r="B60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未启动</x:t>
-        </x:is>
+      <x:c r="B60" s="3" t="str">
+        <x:v>未完成</x:v>
       </x:c>
       <x:c r="C60" s="3" t="inlineStr">
         <x:is>
@@ -13426,7 +13425,13 @@
 2026-09-15 当前源码 QA 追加：All 5/5（WB/API/BB/GR/SEC、隔离 PERF、WEB/UI/UCD/COMP/FLOW、lint、Chromium admin/developer/viewer），PERF smoke/pressure 3/3；GA 14/14、协议/默认路由 24/24。formal11 运行约3531秒/0 errors，要求259200秒，不计为GA；付费订阅/权益、企业治理/私有Gateway、六方会签/回滚/对账和HEAD/origin仍缺证据。索引 outputs/prd148-current-evidence-index-final-20260915.json。
 2026-09-18 当前源码页面域审计 69/69；PAGE-116 Workspace Cookie 本地模型页修复；证据 outputs/prd148-domain-ui-audit-current-20260918-r4/report.json。PRD-148 未完成，见 outputs/prd148-current-evidence-index-final-20260916.json。
 2026-09-18 资源摘要同步后的当前源码页面域审计 69/69；PAGE-116 Workspace Cookie 本地模型页修复；源码 0143b226e96aac094667d32d03e2fe3aef590369c1cdb99aafc262f1e65d9384，生产摘要 aa58650f6c0b3c7badaaa4c69f5f05cd8717f54bec32ab3187c10894518f318b，证据 outputs/prd148-domain-ui-audit-current-20260918-r5/report.json。PRD-148 未完成，见 outputs/prd148-current-evidence-index-final-20260916.json。
-2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。</x:v>
+2026-09-24 当前成员撤权与角色化后台复核：成员移除会在同一事务停用个人 KEY、管理员分配 KEY、历史使用者关联和活动 Workspace session，旧凭据的 Gateway 鉴权立即拒绝；成员/使用者 9/9、Virtual Key 6/6、员工跨协议身份计量停用 1/1、Console 角色与 KEY 287/287 通过。当前源码 SHA256 0ff3be1ea56fee196b21ce6b20ff00f6c144429034956833a426e59aa0182d4f，生产资源摘要 be5564c28378fe2ab5e2d73c5c7bcd8efab194d4c87444c5010abb0bf2d2d87f。Gateway 宽集成因迁移夹具性能未形成 JUnit 终态；局部回归、本地健康和短时运行不构成 GA。按用户决定不执行 72 小时稳定性观察和六方会签，PRD-148 保持未完成。证据：outputs/prd148-member-key-current-20260924.json。
+2026-09-26 r44 中文用户使用容易度复验：r43 三角色分片截图 180/180 作为 r42 源码历史视觉基线保留；r44 当前源码组织 KEY 目标页三角色通过，管理员、开发者、查看者关键交互通过；组织 KEY 桌面操作列修复并完成 1440px 视觉复核；源码 SHA256 ab28d34b317b8cfa94d2980f577a9100facc3a4a44625206b9306d918850fc1f，生产资源摘要 73cafd62584c2c9c5e17a06ca31831a595d109985d6b47d2fae96015385e64bf。真实业务链路、GA门禁和用户已取消的72小时/会签仍未闭合，PRD-148 保持未完成。证据 outputs/prd148-current-evidence-index-final-20260926.json、outputs/prd148-screenshot-visual-audit-20260926-r44.json、.artifacts/product-qa/20260926-key-fix-r44/。
+2026-09-26 r45 用户使用容易度复验：当前源码 63c7dc9230d8154d2624146d9217a734b6e28bdbb99df06a80f6ab84d875e37d；定向角色审计 15/15、可逆交互 15/15 通过，管理员/开发者/查看者分别覆盖组织概览、成员、模型服务、组织或个人 KEY；空区域折叠、搜索表格、自定义接入收起和权限回退均可用。单测 2259/2259、lint 842 files、生产构建 295 assets，资源摘要 3a73b84e5fa3b021cc5b55ca3959ebda80ae17a00214a0f3f33be7001069dd53。证据索引 outputs/prd148-current-evidence-index-final-20260926.json；截图/报告 .artifacts/product-qa/20260926-usability-current-r45/、.artifacts/product-qa/20260926-usability-human-r45/。本批仍不构成真实客户验收或 PRD-148 完成。
+2026-09-28 当前源码 UI 信息清理与相关界面重设计：普通组织页面已移除请求/追踪编号、数据库 ID、区域/认证代码、修订/哈希、模型能力和上下文等内部字段；Provider 目录将自定义中转站并入“添加模型服务”，模型与 Provider 页面改用用户可理解名称并收起高级异常处理。定向前端回归 77/77、lint 842 files、build 295 assets；生产资源摘要 cf4788b50da3257401ed81ff2ba50f1813cfd5d3e8494965bc12d2850553b95c。审查统计见 docs/operations/user-facing-internal-metadata-audit-20260928.md 与 outputs/user-facing-internal-metadata-audit-20260928.json。真实注册到 Gateway/计量/撤权、发布后复核、回滚、财务/隐私/安全/迁移对账、HEAD/origin 仍缺当前证据；用户决定不执行 72 小时观察和六方会签，PRD-148 保持未完成。当前源码与完整证据索引待本轮生成。
+2026-09-28 当前源码 UI 信息清理与相关页面重设计：普通组织页面已移除请求/追踪编号、数据库 ID、区域/认证代码、修订/哈希、模型能力和上下文等内部字段；Provider 目录将自定义中转站并入“添加模型服务”，模型与 Provider 页面改用用户可理解名称并收起高级异常处理。定向前端回归 77/77、lint 842 files、build 295 assets；生产资源摘要 cf4788b50da3257401ed81ff2ba50f1813cfd5d3e8494965bc12d2850553b95c。审查统计见 docs/operations/user-facing-internal-metadata-audit-20260928.md 与 outputs/user-facing-internal-metadata-audit-20260928.json。当前源码 SHA256 f2e2b4be88653c716811b3b44386ae69c890a5a28e1e91d3d41869cc0294a71c（2706 files），证据索引 outputs/prd148-current-evidence-index-final-20260928-r8.json。真实注册到 Gateway/计量/撤权、发布后复核、回滚、财务/隐私/安全/迁移对账、HEAD/origin 仍缺当前证据；用户决定不执行 72 小时观察和六方会签，PRD-148 保持未完成。
+2026-09-28 最终当前绑定修正：manifest 同步后生产资源摘要为 b7012aa806c15ad100ce7b79946e48ace8262fde5f2a9481efb982fbf3cae005，构建 295 assets 与控制面摘要契约 1/1 通过；当前源码快照 outputs/prd148-source-current-20260928-ui-metadata-r4.json，SHA256 710236daf5dae5ed70bdd1d58265c9e9e2998baf79cd13f0ecc2ac805baeaa62（2706 files）；当前证据索引 outputs/prd148-current-evidence-index-final-20260928-r9.json。PRD-148 仍未完成。
+2026-09-28 定向回归最终计数：Provider/模型/目录/走查组合为 85/85，通过命令见 outputs/prd148-current-evidence-index-final-20260928-r10.json；lint 842 files、build 295 assets、资源摘要 b7012aa806c15ad100ce7b79946e48ace8262fde5f2a9481efb982fbf3cae005。此项仍只证明当前源码 UI 回归，PRD-148 保持未完成。\n2026-09-29 文案二次收口：普通用户界面移除重复协议路径、KEY 管理和自定义接入用途说明；文案审计 16 候选（2 必要、14 复核），定向单测 88/88、lint 842 files、生产构建 295 assets；源码 c2f8fb1dbf2ea88c53b995eb958b28e2f044aeb1b51bbc14a2fb090dd30eb9cb，资源摘要 eacf5b43d363109984db023a328731900e5f10586ef4c296ec0a5de0403b77c7；pytest manifest 单项因当前环境缺少 pytest 未执行。PRD-148 未完成。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
